--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>53</v>
       </c>
       <c r="T3" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="U3" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         <v>52</v>
       </c>
       <c r="T4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         <v>22</v>
       </c>
       <c r="T9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3060,155 +3060,155 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3716,42 +3716,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3765,10 +3769,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3781,19 +3785,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3808,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3821,46 +3825,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45991</v>
+        <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3930,46 +3930,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3983,10 +3979,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3999,19 +3995,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4026,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4039,42 +4035,46 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46239</v>
+        <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4144,35 +4144,35 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44761</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5114,8 +5114,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5158,7 +5163,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5188,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5231,7 +5236,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5245,10 +5250,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44526</v>
+        <v>45796</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5261,7 +5266,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5304,7 +5309,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5318,10 +5323,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45251</v>
+        <v>45279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5334,7 +5339,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5377,7 +5382,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45425</v>
+        <v>44643</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5406,13 +5411,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45740</v>
+        <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46091</v>
+        <v>45209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5597,11 +5597,31 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
+      <c r="Z49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5615,10 +5635,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45209</v>
+        <v>45070</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5631,7 +5651,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5670,31 +5690,11 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
-      <c r="Z50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45070</v>
+        <v>45740</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45121</v>
+        <v>46091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5840,7 +5840,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45991</v>
+        <v>45425</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5869,8 +5869,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5913,7 +5918,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5927,10 +5932,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5943,7 +5948,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5986,7 +5991,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6000,10 +6005,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45936</v>
+        <v>45991</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6016,7 +6021,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6059,7 +6064,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6073,10 +6078,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6088,13 +6093,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45324</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6166,13 +6166,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6215,7 +6210,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45839</v>
+        <v>45425</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6244,8 +6239,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6288,7 +6288,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45418</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45610</v>
+        <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45089</v>
+        <v>45763</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6517,14 +6517,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45775</v>
+        <v>46185</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45425</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6609,8 +6609,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46183</v>
+        <v>46239</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45302</v>
+        <v>45439</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6809,14 +6814,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46185</v>
+        <v>45333</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6828,8 +6833,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6872,7 +6882,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6886,10 +6896,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6902,7 +6912,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6945,7 +6955,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>44526</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6975,7 +6985,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7018,7 +7028,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7032,10 +7042,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>45121</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7048,7 +7058,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7091,7 +7101,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7105,10 +7115,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45425</v>
+        <v>45743</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7120,13 +7130,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7169,7 +7174,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7183,10 +7188,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46239</v>
+        <v>45775</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7199,7 +7204,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7242,7 +7247,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7256,10 +7261,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44526</v>
+        <v>45281</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7272,7 +7277,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7315,7 +7320,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7329,10 +7334,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44643</v>
+        <v>45302</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7345,7 +7350,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7388,7 +7393,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7402,10 +7407,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45351</v>
+        <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7417,13 +7422,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45085</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>45610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45363</v>
+        <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7641,8 +7641,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7685,7 +7690,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7699,10 +7704,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>45048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7715,7 +7720,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7758,7 +7763,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7772,10 +7777,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>45089</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7787,13 +7792,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45743</v>
+        <v>45679</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45796</v>
+        <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45279</v>
+        <v>44526</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8065,14 +8065,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45813</v>
+        <v>45763</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3060,155 +3060,155 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3716,46 +3716,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3769,10 +3765,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3785,19 +3781,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3812,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3825,42 +3821,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46239</v>
+        <v>45991</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3930,42 +3930,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3979,10 +3983,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3995,19 +3999,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4022,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4035,46 +4039,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45259</v>
+        <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4144,35 +4144,35 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44643</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44806</v>
+        <v>44761</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,13 +5036,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5085,7 +5080,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45324</v>
+        <v>44806</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5116,11 +5111,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5163,7 +5158,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5188,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5236,7 +5231,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5250,10 +5245,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45796</v>
+        <v>45302</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5266,7 +5261,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5309,7 +5304,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5323,10 +5318,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45279</v>
+        <v>45048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5339,7 +5334,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44643</v>
+        <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5412,7 +5407,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5455,7 +5450,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5465,14 +5460,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45813</v>
+        <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5485,7 +5480,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5528,7 +5523,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45209</v>
+        <v>44526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5558,7 +5553,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5597,31 +5592,11 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
-      <c r="Z49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5635,10 +5610,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45070</v>
+        <v>45281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5651,7 +5626,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5694,7 +5669,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5708,10 +5683,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45740</v>
+        <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5723,8 +5698,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5767,7 +5747,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5781,10 +5761,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46091</v>
+        <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5797,7 +5777,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5840,7 +5820,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5854,10 +5834,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5869,13 +5849,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5918,7 +5893,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5932,10 +5907,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45839</v>
+        <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5947,8 +5922,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5991,7 +5971,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6005,10 +5985,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45991</v>
+        <v>45839</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6021,7 +6001,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6064,7 +6044,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6078,10 +6058,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45936</v>
+        <v>44526</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6094,7 +6074,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6137,7 +6117,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6151,10 +6131,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>45991</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6167,7 +6147,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6210,7 +6190,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6224,10 +6204,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45425</v>
+        <v>45610</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6239,13 +6219,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6288,7 +6263,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6302,10 +6277,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45209</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6318,7 +6293,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6357,11 +6332,31 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
+      <c r="Z59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6375,10 +6370,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46183</v>
+        <v>45070</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6391,7 +6386,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6434,7 +6429,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6448,10 +6443,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45763</v>
+        <v>45121</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6464,7 +6459,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6507,7 +6502,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6517,14 +6512,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46185</v>
+        <v>45439</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6537,7 +6532,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6580,7 +6575,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6594,10 +6589,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45425</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6609,13 +6604,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6658,7 +6648,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6672,10 +6662,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46239</v>
+        <v>44643</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6688,7 +6678,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6731,7 +6721,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6745,10 +6735,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45439</v>
+        <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6761,7 +6751,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6804,7 +6794,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6814,14 +6804,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45333</v>
+        <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6833,13 +6823,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6882,7 +6867,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6896,10 +6881,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45454</v>
+        <v>45425</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6911,8 +6896,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6955,7 +6945,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44526</v>
+        <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6984,8 +6974,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7028,7 +7023,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7042,10 +7037,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45121</v>
+        <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7055,6 +7050,11 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -7101,7 +7101,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45743</v>
+        <v>45085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45775</v>
+        <v>45454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45281</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45302</v>
+        <v>45363</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45085</v>
+        <v>45418</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45610</v>
+        <v>45775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45351</v>
+        <v>45610</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7641,13 +7641,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7690,7 +7685,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7704,10 +7699,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45048</v>
+        <v>45333</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7719,8 +7714,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45089</v>
+        <v>45743</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45679</v>
+        <v>45796</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45418</v>
+        <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7992,14 +7992,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44526</v>
+        <v>45813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8069,10 +8069,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45763</v>
+        <v>45740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3060,155 +3060,155 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3716,42 +3716,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3765,10 +3769,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3781,19 +3785,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3808,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3821,46 +3825,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45991</v>
+        <v>44966</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3930,46 +3930,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4039,35 +4039,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>44761</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44761</v>
+        <v>44806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,8 +5036,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44806</v>
+        <v>45363</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5109,13 +5114,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45763</v>
+        <v>45324</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5187,8 +5187,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5231,7 +5236,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5245,10 +5250,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45302</v>
+        <v>44643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5261,7 +5266,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5304,7 +5309,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5318,10 +5323,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45048</v>
+        <v>45279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5334,7 +5339,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5377,7 +5382,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45763</v>
+        <v>45209</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5407,7 +5412,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5446,11 +5451,31 @@
         <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr"/>
+      <c r="Z47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5460,14 +5485,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46091</v>
+        <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5480,7 +5505,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5523,7 +5548,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5537,10 +5562,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44526</v>
+        <v>45070</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5553,7 +5578,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5596,7 +5621,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5610,10 +5635,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45281</v>
+        <v>45740</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5626,7 +5651,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5669,7 +5694,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5686,7 +5711,7 @@
         <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5704,7 +5729,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5747,7 +5772,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5761,10 +5786,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45251</v>
+        <v>45991</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5777,7 +5802,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5820,7 +5845,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5834,10 +5859,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45936</v>
+        <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5850,7 +5875,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5910,7 +5935,7 @@
         <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5971,7 +5996,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5985,10 +6010,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45839</v>
+        <v>45763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6001,7 +6026,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6044,7 +6069,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6058,10 +6083,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44526</v>
+        <v>45425</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6073,8 +6098,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6117,7 +6147,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6131,10 +6161,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45991</v>
+        <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6147,7 +6177,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6190,7 +6220,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6204,10 +6234,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45610</v>
+        <v>45333</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6219,8 +6249,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6263,7 +6298,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6277,10 +6312,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45209</v>
+        <v>45839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6293,7 +6328,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6332,31 +6367,11 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
-      <c r="Z59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6370,10 +6385,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45070</v>
+        <v>45454</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6386,7 +6401,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6429,7 +6444,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6443,10 +6458,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45121</v>
+        <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6459,7 +6474,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6502,7 +6517,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6516,10 +6531,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45439</v>
+        <v>45936</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6532,7 +6547,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6575,7 +6590,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6589,10 +6604,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6605,7 +6620,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6648,7 +6663,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6662,10 +6677,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44643</v>
+        <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6678,7 +6693,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6721,7 +6736,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6735,10 +6750,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46183</v>
+        <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6751,7 +6766,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6794,7 +6809,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6804,14 +6819,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46185</v>
+        <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6824,7 +6839,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6867,7 +6882,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6881,10 +6896,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45425</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6896,13 +6911,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6945,7 +6955,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45324</v>
+        <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6974,13 +6984,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7023,7 +7028,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7037,10 +7042,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45351</v>
+        <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7052,13 +7057,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7101,7 +7101,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45085</v>
+        <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45454</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>46171</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45363</v>
+        <v>45351</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7349,8 +7349,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7393,7 +7398,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7407,10 +7412,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45418</v>
+        <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7423,7 +7428,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7466,7 +7471,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7476,14 +7481,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45089</v>
+        <v>46185</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7496,7 +7501,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7539,7 +7544,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7553,10 +7558,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45775</v>
+        <v>45048</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7569,7 +7574,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7612,7 +7617,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45610</v>
+        <v>45089</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7642,7 +7647,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7685,7 +7690,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7699,10 +7704,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45333</v>
+        <v>45679</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7714,13 +7719,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45743</v>
+        <v>45418</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45796</v>
+        <v>44526</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45279</v>
+        <v>45763</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7992,14 +7992,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45813</v>
+        <v>46239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8069,10 +8069,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45740</v>
+        <v>45796</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         <v>52</v>
       </c>
       <c r="T4" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="U4" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3060,155 +3060,155 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3716,46 +3716,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3769,10 +3765,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3785,19 +3781,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3812,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3825,42 +3821,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,19 +3890,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3930,46 +3930,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3983,10 +3979,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45259</v>
+        <v>45991</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3999,7 +3995,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4039,35 +4035,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         <v>44806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45363</v>
+        <v>45679</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45324</v>
+        <v>45763</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5187,13 +5187,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5236,7 +5231,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5250,10 +5245,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44643</v>
+        <v>44526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5266,7 +5261,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5309,7 +5304,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5323,10 +5318,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45279</v>
+        <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5339,7 +5334,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45209</v>
+        <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5412,7 +5407,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5451,31 +5446,11 @@
         <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr"/>
-      <c r="Z47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5485,14 +5460,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45813</v>
+        <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5504,8 +5479,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5548,7 +5528,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5562,10 +5542,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45070</v>
+        <v>45740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5578,7 +5558,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5621,7 +5601,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5635,10 +5615,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45740</v>
+        <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5651,7 +5631,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5694,7 +5674,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5708,10 +5688,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45425</v>
+        <v>45209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5723,13 +5703,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5768,11 +5743,31 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
+      <c r="Z51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5786,10 +5781,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45991</v>
+        <v>45070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5802,7 +5797,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5845,7 +5840,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5859,10 +5854,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46091</v>
+        <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5875,7 +5870,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5918,7 +5913,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5932,10 +5927,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45425</v>
+        <v>45839</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5947,13 +5942,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5996,7 +5986,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6010,10 +6000,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45763</v>
+        <v>45439</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6026,7 +6016,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6069,7 +6059,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6083,10 +6073,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45425</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6098,13 +6088,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6147,7 +6132,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6161,10 +6146,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45439</v>
+        <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6176,8 +6161,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6220,7 +6210,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6234,10 +6224,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45333</v>
+        <v>45324</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6255,7 +6245,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6298,7 +6288,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6312,10 +6302,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45839</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6328,7 +6318,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6371,7 +6361,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6385,10 +6375,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45454</v>
+        <v>45418</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6401,7 +6391,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6444,7 +6434,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6458,10 +6448,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44526</v>
+        <v>46183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6474,7 +6464,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6517,7 +6507,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6527,14 +6517,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45936</v>
+        <v>46185</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6547,7 +6537,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6590,7 +6580,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6604,10 +6594,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45610</v>
+        <v>45089</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6620,7 +6610,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6663,7 +6653,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6677,10 +6667,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45121</v>
+        <v>45775</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6693,7 +6683,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6736,7 +6726,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6750,10 +6740,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>45991</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6766,7 +6756,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6809,7 +6799,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6823,10 +6813,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45775</v>
+        <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6839,7 +6829,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6882,7 +6872,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6912,7 +6902,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6955,7 +6945,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45302</v>
+        <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6985,7 +6975,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7028,7 +7018,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7042,10 +7032,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45085</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7058,7 +7048,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7101,7 +7091,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7115,10 +7105,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45251</v>
+        <v>45425</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7130,8 +7120,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7174,7 +7169,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7188,10 +7183,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>44526</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7204,7 +7199,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7247,7 +7242,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7261,10 +7256,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46171</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7277,7 +7272,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7320,7 +7315,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7334,10 +7329,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45351</v>
+        <v>44643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7349,13 +7344,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7398,7 +7388,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7412,10 +7402,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46183</v>
+        <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7425,6 +7415,11 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -7471,7 +7466,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7481,14 +7476,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46185</v>
+        <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7501,7 +7496,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7544,7 +7539,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7558,10 +7553,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45048</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7574,7 +7569,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7617,7 +7612,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7631,10 +7626,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45089</v>
+        <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7647,7 +7642,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7690,7 +7685,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7704,10 +7699,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45679</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7720,7 +7715,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7763,7 +7758,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7777,10 +7772,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45418</v>
+        <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7792,8 +7787,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44526</v>
+        <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45763</v>
+        <v>45796</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46239</v>
+        <v>45279</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8065,14 +8065,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45796</v>
+        <v>45813</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17454-2026</t>
+          <t>A 59567-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46120</v>
+        <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -2246,9 +2246,140 @@
         <v>32</v>
       </c>
       <c r="U13" t="n">
+        <v>27</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Fjällig taggsvamp s.str.
+Kandelabersvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vintertagging
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Brandticka
+Grovticka
+Grön sköldmossa
+Jättesvampmal
+Mindre märgborre
+Vågbandad barkbock
+Spillkråka
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17454-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32</v>
+      </c>
+      <c r="U14" t="n">
         <v>24</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -2271,168 +2402,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 59567-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>16</v>
-      </c>
-      <c r="T14" t="n">
-        <v>28</v>
-      </c>
-      <c r="U14" t="n">
-        <v>23</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kandelabersvamp
-Tallticka
-Talltita
-Ullticka
-Vintertagging
-Vågticka
-Björksplintborre
-Brandticka
-Grovticka
-Grön sköldmossa
-Jättesvampmal
-Mindre märgborre
-Vågbandad barkbock
-Spillkråka
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
         <v/>
       </c>
     </row>
@@ -2456,7 +2459,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2575,7 +2578,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2685,7 +2688,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2798,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2905,7 +2908,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2997,7 +3000,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3007,14 +3010,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3027,13 +3030,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3060,155 +3063,155 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3235,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3343,7 +3346,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3448,7 +3451,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3553,7 +3556,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3649,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3660,10 +3663,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3676,20 +3679,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3700,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3716,42 +3719,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3765,10 +3768,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44966</v>
+        <v>45991</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3781,7 +3784,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3790,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3805,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3821,46 +3824,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3874,10 +3877,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,19 +3893,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3917,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3930,42 +3933,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3979,10 +3986,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3995,7 +4002,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4035,39 +4042,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4094,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4196,7 +4199,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4274,7 +4277,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4355,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4425,7 +4428,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4501,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4571,7 +4574,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4649,7 +4652,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4725,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4800,7 +4803,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4881,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4954,7 @@
         <v>44761</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5024,7 +5027,7 @@
         <v>44806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5085,7 +5088,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5099,10 +5102,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5114,8 +5117,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5158,7 +5166,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5172,10 +5180,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5188,7 +5196,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5231,7 +5239,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5245,10 +5253,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44526</v>
+        <v>44643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5261,7 +5269,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5304,7 +5312,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5318,10 +5326,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46091</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5334,7 +5342,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5373,11 +5381,31 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
+      <c r="Z46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5391,10 +5419,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45251</v>
+        <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5407,7 +5435,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5450,7 +5478,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5467,7 +5495,7 @@
         <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5485,7 +5513,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5528,7 +5556,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5542,10 +5570,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45740</v>
+        <v>45839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5558,7 +5586,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5618,7 +5646,7 @@
         <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5674,7 +5702,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5688,10 +5716,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45209</v>
+        <v>45610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5743,31 +5771,11 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
-      <c r="Z51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5781,10 +5789,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45070</v>
+        <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5796,8 +5804,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5840,7 +5853,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5854,10 +5867,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45121</v>
+        <v>45763</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5870,7 +5883,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5913,7 +5926,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5927,10 +5940,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45839</v>
+        <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5942,8 +5955,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6003,7 +6021,7 @@
         <v>45439</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6059,7 +6077,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6073,10 +6091,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45333</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6088,8 +6106,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6132,7 +6155,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6146,10 +6169,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45425</v>
+        <v>45454</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6161,13 +6184,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6210,7 +6228,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6224,10 +6242,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45324</v>
+        <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6239,13 +6257,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6288,7 +6301,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6302,10 +6315,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6318,7 +6331,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6361,7 +6374,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6375,10 +6388,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45418</v>
+        <v>45121</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6391,7 +6404,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6434,7 +6447,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6448,10 +6461,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46183</v>
+        <v>45743</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6464,7 +6477,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6507,7 +6520,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6517,14 +6530,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46185</v>
+        <v>45775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6537,7 +6550,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6580,7 +6593,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6594,10 +6607,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45089</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6610,7 +6623,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6653,7 +6666,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6667,10 +6680,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45775</v>
+        <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6683,7 +6696,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6726,7 +6739,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6740,10 +6753,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45991</v>
+        <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6756,7 +6769,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6799,7 +6812,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6813,10 +6826,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45302</v>
+        <v>45251</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6829,7 +6842,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6872,7 +6885,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6886,10 +6899,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>46171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6902,7 +6915,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6945,7 +6958,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6959,10 +6972,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6975,7 +6988,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7018,7 +7031,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7032,10 +7045,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>46183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7048,7 +7061,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7091,7 +7104,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7105,10 +7118,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45425</v>
+        <v>45351</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7126,7 +7139,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7169,7 +7182,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7179,14 +7192,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44526</v>
+        <v>46185</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7199,7 +7212,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7242,7 +7255,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7256,10 +7269,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>46091</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7272,7 +7285,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7315,7 +7328,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7329,10 +7342,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44643</v>
+        <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7345,7 +7358,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7388,7 +7401,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7402,10 +7415,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45351</v>
+        <v>45089</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7417,13 +7430,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7466,7 +7474,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7480,10 +7488,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45085</v>
+        <v>45679</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7496,7 +7504,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7539,7 +7547,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7553,10 +7561,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>45418</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7569,7 +7577,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7612,7 +7620,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7626,10 +7634,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45363</v>
+        <v>44526</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7642,7 +7650,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7685,7 +7693,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7699,10 +7707,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>45763</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7715,7 +7723,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7758,7 +7766,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7772,10 +7780,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>46239</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7787,13 +7795,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7836,7 +7839,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7850,10 +7853,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45743</v>
+        <v>45796</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7866,7 +7869,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7909,7 +7912,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7923,10 +7926,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45796</v>
+        <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7939,7 +7942,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7982,7 +7985,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7992,14 +7995,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45279</v>
+        <v>45813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8012,7 +8015,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8055,7 +8058,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8065,14 +8068,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45813</v>
+        <v>45740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8085,7 +8088,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8148,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>53</v>
       </c>
       <c r="T3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46043</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         <v>52</v>
       </c>
       <c r="T4" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="U4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>21</v>
@@ -1156,13 +1156,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T5" t="n">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="U5" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1193,13 +1193,16 @@
 Blomkålssvamp
 Blåmossa
 Bronshjon
+Flagellkvastmossa
 Granbarkgnagare
 Grovticka
 Grön sköldmossa
 Grönpyrola
 Mindre märgborre
 Rödgul trumpetsvamp
+Skogshakmossa
 Vedticka
+Linnea
 Spillkråka
 Tjäder
 Fiskgjuse
@@ -1264,7 +1267,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1402,7 +1405,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1541,7 +1544,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,7 +1678,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1805,7 +1808,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1938,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2071,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2197,7 +2200,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2328,7 +2331,7 @@
         <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2459,7 +2462,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2578,7 +2581,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2688,7 +2691,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2798,7 +2801,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2908,7 +2911,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3017,7 +3020,7 @@
         <v>46199</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3128,7 +3131,7 @@
         <v>45014</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3235,7 +3238,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3346,7 +3349,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3451,7 +3454,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3556,7 +3559,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3666,7 +3669,7 @@
         <v>44796</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3771,7 +3774,7 @@
         <v>45991</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3880,7 +3883,7 @@
         <v>44966</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3992,7 @@
         <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4094,7 +4097,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4199,7 +4202,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4277,7 +4280,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4355,7 +4358,7 @@
         <v>44460</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4428,7 +4431,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4501,7 +4504,7 @@
         <v>44845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4574,7 +4577,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4652,7 +4655,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4725,7 +4728,7 @@
         <v>44476</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4806,7 @@
         <v>44825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4881,7 +4884,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4954,7 +4957,7 @@
         <v>44761</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5027,7 +5030,7 @@
         <v>44806</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5105,7 +5108,7 @@
         <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5183,7 +5186,7 @@
         <v>45363</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5256,7 +5259,7 @@
         <v>44643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5329,7 +5332,7 @@
         <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5425,7 @@
         <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5495,7 +5498,7 @@
         <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5573,7 +5576,7 @@
         <v>45839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5646,7 +5649,7 @@
         <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5719,7 +5722,7 @@
         <v>45610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5792,7 +5795,7 @@
         <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5870,7 +5873,7 @@
         <v>45763</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5943,7 +5946,7 @@
         <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6021,7 +6024,7 @@
         <v>45439</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6094,7 +6097,7 @@
         <v>45333</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6172,7 +6175,7 @@
         <v>45454</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6245,7 +6248,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6318,7 +6321,7 @@
         <v>45991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6391,7 +6394,7 @@
         <v>45121</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6464,7 +6467,7 @@
         <v>45743</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6537,7 +6540,7 @@
         <v>45775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6610,7 +6613,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6683,7 +6686,7 @@
         <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6756,7 +6759,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6829,7 +6832,7 @@
         <v>45251</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6902,7 +6905,7 @@
         <v>46171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6975,7 +6978,7 @@
         <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7048,7 +7051,7 @@
         <v>46183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7121,7 +7124,7 @@
         <v>45351</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7199,7 +7202,7 @@
         <v>46185</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7272,7 +7275,7 @@
         <v>46091</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7345,7 +7348,7 @@
         <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7418,7 +7421,7 @@
         <v>45089</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7491,7 +7494,7 @@
         <v>45679</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7564,7 +7567,7 @@
         <v>45418</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7637,7 +7640,7 @@
         <v>44526</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7710,7 +7713,7 @@
         <v>45763</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7783,7 +7786,7 @@
         <v>46239</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7856,7 +7859,7 @@
         <v>45796</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7929,7 +7932,7 @@
         <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8002,7 +8005,7 @@
         <v>45813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8075,7 +8078,7 @@
         <v>45740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8148,7 +8151,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE84"/>
+  <dimension ref="A1:AE83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,24 +767,24 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3151-2025</t>
+          <t>S 152-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -821,21 +821,196 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R3" t="n">
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="U3" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Goliatmusseron
+Gränsticka
+Jättemusseron
+Knärot
+Lakritsmusseron
+Rotfingersvamp
+Apelsinticka
+Blå taggsvamp
+Brunlångöra
+Dropptaggsvamp
+Fyrflikig jordstjärna
+Gelatinfingersvamp
+Lunglav
+Motaggsvamp
+Nordfladdermus
+Orange taggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Björksplintborre
+Blomkålssvamp
+Blåmossa
+Bronshjon
+Flagellkvastmossa
+Fällmossa
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Jättesvampmal
+Mindre märgborre
+Nästlav
+Plattlummer
+Rödgul trumpetsvamp
+Spindelblomster
+Stubbspretmossa
+Thomsons trägnagare
+Trådticka
+Vedticka
+Västlig hakmossa
+Vågbandad barkbock
+Krushättemossa
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Större brunfladdermus
+Trollpipistrell
+Vattenfladdermus
+Kopparödla
+Mindre vattensalamander
+Vanlig groda
+Vanlig padda
+Vanlig snok
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/S 152-2026 artfynd.xlsx", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/S 152-2026 karta.png", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/S 152-2026 georefererad karta.tif", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/S 152-2026 karta knärot.png", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/S 152-2026 FSC-klagomål.docx", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/S 152-2026 FSC-klagomål mail.docx", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/S 152-2026 tillsynsbegäran.docx", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/S 152-2026 tillsynsbegäran mail.docx", "S 152-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/S 152-2026 prioriterade fågelarter.docx", "S 152-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 3151-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45679</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>58</v>
+      </c>
+      <c r="T4" t="n">
+        <v>259</v>
+      </c>
+      <c r="U4" t="n">
+        <v>168</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Goliatmusseron
@@ -844,11 +1019,13 @@
 Knärot
 Ringlav
 Rotfingersvamp
+Brunlångöra
 Dropptaggsvamp
 Fjällig taggsvamp s.str.
 Fyrflikig jordstjärna
 Mindre hackspett
 Motaggsvamp
+Nordfladdermus
 Reliktbock
 Skarp dropptaggsvamp
 Talltagel
@@ -884,6 +1061,9 @@
 Spillkråka
 Tjäder
 Tofsmes
+Dvärgpipistrell
+Större brunfladdermus
+Vattenfladdermus
 Åkergroda
 Vanlig groda
 Vanlig padda
@@ -892,204 +1072,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 3151-2025 artfynd.xlsx", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 3151-2025 karta.png", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 3151-2025 georefererad karta.tif", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 3151-2025 karta knärot.png", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 3151-2025 FSC-klagomål.docx", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 3151-2025 FSC-klagomål mail.docx", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 3151-2025 tillsynsbegäran.docx", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 3151-2025 tillsynsbegäran mail.docx", "A 3151-2025")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 3151-2025 prioriterade fågelarter.docx", "A 3151-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S 152-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46043</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>52</v>
-      </c>
-      <c r="T4" t="n">
-        <v>205</v>
-      </c>
-      <c r="U4" t="n">
-        <v>70</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Goliatmusseron
-Gränsticka
-Jättemusseron
-Knärot
-Lakritsmusseron
-Rotfingersvamp
-Apelsinticka
-Blå taggsvamp
-Dropptaggsvamp
-Fyrflikig jordstjärna
-Gelatinfingersvamp
-Lunglav
-Motaggsvamp
-Orange taggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Ullticka
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Björksplintborre
-Blomkålssvamp
-Blåmossa
-Bronshjon
-Fällmossa
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Jättesvampmal
-Mindre märgborre
-Nästlav
-Plattlummer
-Rödgul trumpetsvamp
-Spindelblomster
-Stubbspretmossa
-Thomsons trägnagare
-Trådticka
-Vedticka
-Västlig hakmossa
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Kopparödla
-Mindre vattensalamander
-Vanlig padda
-Vanlig snok
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/S 152-2026 artfynd.xlsx", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/S 152-2026 karta.png", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/S 152-2026 georefererad karta.tif", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/S 152-2026 karta knärot.png", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/S 152-2026 FSC-klagomål.docx", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/S 152-2026 FSC-klagomål mail.docx", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/S 152-2026 tillsynsbegäran.docx", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/S 152-2026 tillsynsbegäran mail.docx", "S 152-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/S 152-2026 prioriterade fågelarter.docx", "S 152-2026")</f>
         <v/>
       </c>
     </row>
@@ -1113,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1129,13 +1145,13 @@
         <v>54.5</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
@@ -1150,19 +1166,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T5" t="n">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="U5" t="n">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1173,6 +1189,7 @@
 Dropptaggsvamp
 Enkelbeckasin
 Fjällig taggsvamp s.str.
+Grönhjon
 Kandelabersvamp
 Kattfotslav
 Kortskaftad ärgspik
@@ -1202,9 +1219,11 @@
 Rödgul trumpetsvamp
 Skogshakmossa
 Vedticka
+Vågbandad barkbock
 Linnea
 Spillkråka
 Tjäder
+Tofsmes
 Fiskgjuse
 Havsörn
 Kungsfågel
@@ -1267,7 +1286,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1405,7 +1424,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1678,7 +1697,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1808,7 +1827,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1938,7 +1957,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2071,7 +2090,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2200,7 +2219,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2331,7 +2350,7 @@
         <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2462,7 +2481,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2581,7 +2600,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2691,7 +2710,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2801,7 +2820,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2911,7 +2930,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3020,7 +3039,7 @@
         <v>46199</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3131,7 +3150,7 @@
         <v>45014</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3238,7 +3257,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3349,7 +3368,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3454,7 +3473,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3578,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3669,7 +3688,7 @@
         <v>44796</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3774,7 +3793,7 @@
         <v>45991</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3883,7 +3902,7 @@
         <v>44966</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3992,7 +4011,7 @@
         <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4097,7 +4116,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4202,7 +4221,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4280,7 +4299,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4341,7 +4360,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50903-2021</t>
+          <t>A 45501-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4355,10 +4374,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44460</v>
+        <v>44845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4371,7 +4390,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4414,7 +4433,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45501-2022</t>
+          <t>A 45498-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4431,7 +4450,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4463,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4487,7 +4506,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45498-2022</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4501,10 +4520,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44845</v>
+        <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4516,8 +4535,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4560,7 +4584,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4570,14 +4594,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44476</v>
+        <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4587,11 +4611,6 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -4638,7 +4657,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4648,14 +4667,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44694</v>
+        <v>44476</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4665,6 +4684,11 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -4711,7 +4735,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4725,10 +4749,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44476</v>
+        <v>44825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4742,11 +4766,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4789,7 +4813,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4803,10 +4827,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44825</v>
+        <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4818,13 +4842,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4867,7 +4886,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4881,10 +4900,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4897,7 +4916,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4940,7 +4959,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4954,10 +4973,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44761</v>
+        <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4969,8 +4988,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5013,7 +5037,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5027,10 +5051,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44806</v>
+        <v>45363</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,13 +5066,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5108,7 +5127,7 @@
         <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5169,7 +5188,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5183,10 +5202,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45363</v>
+        <v>44643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5199,7 +5218,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5242,7 +5261,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5256,10 +5275,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44643</v>
+        <v>45209</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5311,11 +5330,31 @@
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
+      <c r="Z45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5329,10 +5368,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45070</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5345,7 +5384,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5384,31 +5423,11 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
-      <c r="Z46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5422,10 +5441,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45070</v>
+        <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5437,8 +5456,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5481,7 +5505,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5495,10 +5519,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45425</v>
+        <v>45839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5510,13 +5534,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5559,7 +5578,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5573,10 +5592,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45839</v>
+        <v>45936</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5589,7 +5608,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5632,7 +5651,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5646,10 +5665,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45936</v>
+        <v>45610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5662,7 +5681,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5705,7 +5724,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5719,10 +5738,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45610</v>
+        <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5734,8 +5753,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5778,7 +5802,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5792,10 +5816,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45425</v>
+        <v>45763</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5807,13 +5831,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5856,7 +5875,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5870,10 +5889,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45763</v>
+        <v>45425</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5885,8 +5904,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5929,7 +5953,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5943,10 +5967,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45425</v>
+        <v>45991</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5958,13 +5982,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6024,7 +6043,7 @@
         <v>45439</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6080,7 +6099,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6094,10 +6113,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45333</v>
+        <v>46171</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6109,13 +6128,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6158,7 +6172,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6172,10 +6186,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45454</v>
+        <v>45333</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6187,8 +6201,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6231,7 +6250,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6245,10 +6264,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44526</v>
+        <v>45454</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6261,7 +6280,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6304,7 +6323,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6318,10 +6337,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45991</v>
+        <v>44526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6334,7 +6353,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6377,7 +6396,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6391,10 +6410,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45121</v>
+        <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6450,7 +6469,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6460,14 +6479,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45743</v>
+        <v>46185</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6480,7 +6499,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6523,7 +6542,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6537,10 +6556,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45775</v>
+        <v>45121</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6553,7 +6572,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6596,7 +6615,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6610,10 +6629,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>45743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6626,7 +6645,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6669,7 +6688,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6683,10 +6702,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45302</v>
+        <v>45775</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6699,7 +6718,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6742,7 +6761,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6756,10 +6775,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45085</v>
+        <v>45281</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6772,7 +6791,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6815,7 +6834,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6829,10 +6848,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45251</v>
+        <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6845,7 +6864,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6888,7 +6907,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6902,10 +6921,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46171</v>
+        <v>45085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6918,7 +6937,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6961,7 +6980,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6975,10 +6994,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>46091</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6991,7 +7010,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7034,7 +7053,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7048,10 +7067,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46183</v>
+        <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7064,7 +7083,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7107,7 +7126,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7121,10 +7140,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45351</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7136,13 +7155,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7185,7 +7199,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7195,14 +7209,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46185</v>
+        <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7214,8 +7228,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7258,7 +7277,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7272,10 +7291,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46091</v>
+        <v>45048</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7288,7 +7307,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7331,7 +7350,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7345,10 +7364,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45048</v>
+        <v>45089</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7361,7 +7380,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7404,7 +7423,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7418,10 +7437,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45089</v>
+        <v>45679</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7434,7 +7453,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7477,7 +7496,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7491,10 +7510,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45679</v>
+        <v>45418</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7507,7 +7526,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7550,7 +7569,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7564,10 +7583,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45418</v>
+        <v>44526</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7580,7 +7599,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7623,7 +7642,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7637,10 +7656,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44526</v>
+        <v>45763</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7653,7 +7672,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7696,7 +7715,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7710,10 +7729,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45763</v>
+        <v>46239</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7726,7 +7745,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7769,7 +7788,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7783,10 +7802,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46239</v>
+        <v>45796</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7799,7 +7818,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7842,7 +7861,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7856,10 +7875,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45796</v>
+        <v>45279</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7872,7 +7891,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7915,7 +7934,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7925,14 +7944,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45279</v>
+        <v>45813</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7945,7 +7964,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7988,7 +8007,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7998,14 +8017,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45813</v>
+        <v>45740</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8018,7 +8037,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8058,27 +8077,27 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="15" customHeight="1">
+    <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>S 1718-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45740</v>
+        <v>46188</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8091,7 +8110,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8130,79 +8149,6 @@
         <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>S 1718-2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E84" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="U3" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>22</v>
@@ -1172,13 +1172,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="U5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1218,6 +1218,7 @@
 Mindre märgborre
 Rödgul trumpetsvamp
 Skogshakmossa
+Thomsons trägnagare
 Vedticka
 Vågbandad barkbock
 Linnea
@@ -1286,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1424,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1680,7 +1681,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59566-2025</t>
+          <t>A 67894-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1694,10 +1695,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45991</v>
+        <v>44525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1710,19 +1711,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
         <v>9</v>
       </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1734,21 +1735,151 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>22</v>
       </c>
       <c r="T9" t="n">
+        <v>48</v>
+      </c>
+      <c r="U9" t="n">
+        <v>48</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Grönhjon
+Kortskaftad ärgspik
+Motaggsvamp
+Reliktbock
+Svartvit taggsvamp
+Tallticka
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blåmossa
+Bronshjon
+Granbarkgnagare
+Grovticka
+Grön sköldmossa
+Kornknutmossa
+Mindre märgborre
+Stor revmossa
+Stubbspretmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 59566-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
         <v>49</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>44</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Rotfingersvamp
@@ -1774,166 +1905,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67894-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44525</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>48</v>
-      </c>
-      <c r="U10" t="n">
-        <v>48</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Grönhjon
-Kortskaftad ärgspik
-Motaggsvamp
-Reliktbock
-Svartvit taggsvamp
-Tallticka
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blåmossa
-Bronshjon
-Granbarkgnagare
-Grovticka
-Grön sköldmossa
-Kornknutmossa
-Mindre märgborre
-Stor revmossa
-Stubbspretmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
         <v/>
       </c>
     </row>
@@ -1957,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2090,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2203,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59567-2025</t>
+          <t>A 17454-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2216,10 +2217,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45991</v>
+        <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2232,16 +2233,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>31.4</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2256,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -2268,9 +2269,140 @@
         <v>32</v>
       </c>
       <c r="U13" t="n">
+        <v>24</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Ullticka
+Barkticka
+Björksplintborre
+Blåmossa
+Blåsfliksmossa
+Granbarkgnagare
+Grön sköldmossa
+Grönpyrola
+Guldlockmossa
+Mindre märgborre
+Thomsons trägnagare
+Västlig hakmossa
+Blåsippa
+Glansfläck
+Skriftlav
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 59567-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32</v>
+      </c>
+      <c r="U14" t="n">
         <v>27</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Fjällig taggsvamp s.str.
@@ -2293,171 +2425,40 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17454-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>11</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>19</v>
-      </c>
-      <c r="T14" t="n">
-        <v>32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>24</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Ullticka
-Barkticka
-Björksplintborre
-Blåmossa
-Blåsfliksmossa
-Granbarkgnagare
-Grön sköldmossa
-Grönpyrola
-Guldlockmossa
-Mindre märgborre
-Thomsons trägnagare
-Västlig hakmossa
-Blåsippa
-Glansfläck
-Skriftlav
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2600,7 +2601,7 @@
         <v>44463</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2710,7 +2711,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2820,7 +2821,7 @@
         <v>44526</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2930,7 +2931,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3022,7 +3023,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3032,14 +3033,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,13 +3053,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -3085,266 +3086,266 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 21231-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Spillkråka
+Trana</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 21231-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Spillkråka
-Trana</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
         <v/>
       </c>
     </row>
@@ -3368,7 +3369,7 @@
         <v>44818</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3473,7 +3474,7 @@
         <v>44580</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3578,7 +3579,7 @@
         <v>44806</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3688,7 +3689,7 @@
         <v>44796</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3776,7 +3777,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3790,10 +3791,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3806,7 +3807,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3846,39 +3847,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3902,7 +3899,7 @@
         <v>44966</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3994,7 +3991,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4008,10 +4005,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45259</v>
+        <v>45991</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4024,7 +4021,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4064,35 +4061,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
@@ -4116,7 +4117,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4221,7 +4222,7 @@
         <v>44825</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4299,7 +4300,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4377,7 +4378,7 @@
         <v>44845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4450,7 +4451,7 @@
         <v>44845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4523,7 +4524,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4601,7 +4602,7 @@
         <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4674,7 +4675,7 @@
         <v>44476</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4752,7 +4753,7 @@
         <v>44825</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4830,7 +4831,7 @@
         <v>44643</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4903,7 +4904,7 @@
         <v>44761</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4976,7 +4977,7 @@
         <v>44806</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5037,7 +5038,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5051,10 +5052,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45363</v>
+        <v>45679</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5067,7 +5068,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5110,7 +5111,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5124,10 +5125,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45324</v>
+        <v>45209</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5139,13 +5140,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5184,11 +5180,31 @@
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
+      <c r="Z43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5202,10 +5218,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44643</v>
+        <v>45070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5218,7 +5234,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5261,7 +5277,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5275,10 +5291,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45209</v>
+        <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5291,7 +5307,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5330,31 +5346,11 @@
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
-      <c r="Z45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5368,10 +5364,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45070</v>
+        <v>45439</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5384,7 +5380,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5427,7 +5423,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5441,10 +5437,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45425</v>
+        <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5456,13 +5452,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5505,7 +5496,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5519,10 +5510,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45839</v>
+        <v>45796</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5535,7 +5526,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5578,7 +5569,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5592,10 +5583,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45936</v>
+        <v>45279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5608,7 +5599,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5651,7 +5642,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5665,10 +5656,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45610</v>
+        <v>45425</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5680,8 +5671,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5724,7 +5720,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5738,10 +5734,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45425</v>
+        <v>44526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5753,13 +5749,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5802,7 +5793,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5816,10 +5807,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45763</v>
+        <v>45324</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5831,8 +5822,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5875,7 +5871,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5889,10 +5885,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45425</v>
+        <v>45418</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5904,13 +5900,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5953,7 +5944,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5963,14 +5954,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45991</v>
+        <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5983,7 +5974,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6026,7 +6017,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6040,10 +6031,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45439</v>
+        <v>45089</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6056,7 +6047,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6099,7 +6090,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6113,10 +6104,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46171</v>
+        <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6129,7 +6120,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6172,7 +6163,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6186,10 +6177,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45333</v>
+        <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6207,7 +6198,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6250,7 +6241,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6264,10 +6255,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45454</v>
+        <v>45775</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6280,7 +6271,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6323,7 +6314,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6337,10 +6328,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44526</v>
+        <v>45991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6353,7 +6344,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6396,7 +6387,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6410,10 +6401,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46183</v>
+        <v>45302</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6426,7 +6417,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6469,7 +6460,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6479,14 +6470,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46185</v>
+        <v>45048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6499,7 +6490,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6542,7 +6533,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6556,10 +6547,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45121</v>
+        <v>45763</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6572,7 +6563,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6615,7 +6606,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6629,10 +6620,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45743</v>
+        <v>46239</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6645,7 +6636,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6688,7 +6679,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6702,10 +6693,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45775</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6718,7 +6709,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6761,7 +6752,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6775,10 +6766,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45281</v>
+        <v>45425</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6790,8 +6781,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6834,7 +6830,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6848,10 +6844,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45302</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6864,7 +6860,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6907,7 +6903,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6921,10 +6917,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45085</v>
+        <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6937,7 +6933,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6980,7 +6976,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6994,10 +6990,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46091</v>
+        <v>44643</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7010,7 +7006,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7053,7 +7049,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7067,10 +7063,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45251</v>
+        <v>45740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7083,7 +7079,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7126,7 +7122,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7140,10 +7136,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>45351</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7155,8 +7151,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7199,7 +7200,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7213,10 +7214,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45351</v>
+        <v>45085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7228,13 +7229,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7277,7 +7273,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7291,10 +7287,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45048</v>
+        <v>45454</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7307,7 +7303,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7350,7 +7346,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7364,10 +7360,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45089</v>
+        <v>45363</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7380,7 +7376,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7423,7 +7419,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7437,10 +7433,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45679</v>
+        <v>45936</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7453,7 +7449,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>6.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7496,7 +7492,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7510,10 +7506,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45418</v>
+        <v>45839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7526,7 +7522,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7569,7 +7565,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7583,10 +7579,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7599,7 +7595,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7642,7 +7638,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7656,10 +7652,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45763</v>
+        <v>45333</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7671,8 +7667,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7715,7 +7716,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7729,10 +7730,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46239</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7745,7 +7746,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7788,7 +7789,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7802,10 +7803,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45796</v>
+        <v>45743</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7818,7 +7819,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7861,7 +7862,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7875,10 +7876,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45279</v>
+        <v>46171</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7891,7 +7892,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7934,7 +7935,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7944,14 +7945,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45813</v>
+        <v>46183</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7964,7 +7965,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8007,7 +8008,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8017,14 +8018,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45740</v>
+        <v>46185</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8037,7 +8038,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8097,7 +8098,7 @@
         <v>46188</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE83"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="U3" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 67894-2021</t>
+          <t>A 59566-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44525</v>
+        <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1735,21 +1735,151 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>22</v>
       </c>
       <c r="T9" t="n">
+        <v>49</v>
+      </c>
+      <c r="U9" t="n">
+        <v>44</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Rotfingersvamp
+Tallkötticka
+Talltita
+Ullticka
+Bronshjon
+Flagellkvastmossa
+Grön sköldmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Stubbspretmossa
+Thomsons trägnagare
+Vedticka
+Ekbräken
+Hultbräken
+Mattlummer
+Spillkråka
+Kungsfågel
+Kopparödla
+Skogsödla
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67894-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44525</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
         <v>48</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>48</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Grönhjon
@@ -1775,166 +1905,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 59566-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>49</v>
-      </c>
-      <c r="U10" t="n">
-        <v>44</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Rotfingersvamp
-Tallkötticka
-Talltita
-Ullticka
-Bronshjon
-Flagellkvastmossa
-Grön sköldmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Stubbspretmossa
-Thomsons trägnagare
-Vedticka
-Ekbräken
-Hultbräken
-Mattlummer
-Spillkråka
-Kungsfågel
-Kopparödla
-Skogsödla
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
         <v/>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17454-2026</t>
+          <t>A 59567-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46120</v>
+        <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,16 +2233,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -2269,9 +2269,140 @@
         <v>32</v>
       </c>
       <c r="U13" t="n">
+        <v>27</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Fjällig taggsvamp s.str.
+Kandelabersvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vintertagging
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Brandticka
+Grovticka
+Grön sköldmossa
+Jättesvampmal
+Mindre märgborre
+Vågbandad barkbock
+Spillkråka
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17454-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32</v>
+      </c>
+      <c r="U14" t="n">
         <v>24</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -2294,171 +2425,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 59567-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>19</v>
-      </c>
-      <c r="T14" t="n">
-        <v>32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>27</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Fjällig taggsvamp s.str.
-Kandelabersvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vintertagging
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Brandticka
-Grovticka
-Grön sköldmossa
-Jättesvampmal
-Mindre märgborre
-Vågbandad barkbock
-Spillkråka
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52616-2021</t>
+          <t>A 68883-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2594,14 +2594,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44463</v>
+        <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2614,19 +2614,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2638,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2650,229 +2650,9 @@
         <v>9</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Grön sköldmossa
-Noshornsoxe
-Stubbspretmossa
-Vågbandad barkbock
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 52616-2021 artfynd.xlsx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 52616-2021 karta.png", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 52616-2021 georefererad karta.tif", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 52616-2021 FSC-klagomål.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 52616-2021 FSC-klagomål mail.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 52616-2021 tillsynsbegäran.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 52616-2021 tillsynsbegäran mail.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 52616-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44463</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>9</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Grön sköldmossa
-Noshornsoxe
-Stubbspretmossa
-Vågbandad barkbock
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 52616-2021 artfynd.xlsx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 52616-2021 karta.png", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 52616-2021 georefererad karta.tif", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 52616-2021 FSC-klagomål.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 52616-2021 FSC-klagomål mail.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 52616-2021 tillsynsbegäran.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 52616-2021 tillsynsbegäran mail.docx", "A 52616-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 68883-2021</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44526</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Kvällsmaskros
 Jungfrulin
@@ -2882,107 +2662,107 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 68883-2021 artfynd.xlsx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 68883-2021 karta.png", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 68883-2021 georefererad karta.tif", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 68883-2021 FSC-klagomål.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 68883-2021 FSC-klagomål mail.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 68883-2021 tillsynsbegäran.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 68883-2021 tillsynsbegäran mail.docx", "A 68883-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 47707-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I17" t="n">
         <v>1.4</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>4</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>5</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T17" t="n">
         <v>10</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U17" t="n">
         <v>8</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Granbarkgnagare
@@ -2991,257 +2771,473 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 47707-2023 artfynd.xlsx", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 47707-2023 karta.png", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 47707-2023 georefererad karta.tif", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 47707-2023 FSC-klagomål.docx", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 47707-2023 FSC-klagomål mail.docx", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 47707-2023 tillsynsbegäran.docx", "A 47707-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 47707-2023 tillsynsbegäran mail.docx", "A 47707-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 14729-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45014</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I19" t="n">
         <v>0.2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 21231-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45779</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I20" t="n">
         <v>4.3</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 39636-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44818</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 39636-2022 artfynd.xlsx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 39636-2022 karta.png", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 39636-2022 georefererad karta.tif", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 39636-2022 FSC-klagomål.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 39636-2022 FSC-klagomål mail.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 39636-2022 tillsynsbegäran.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 39636-2022 tillsynsbegäran mail.docx", "A 39636-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 2722-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3251,14 +3247,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46199</v>
+        <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3271,7 +3267,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3280,79 +3276,73 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 39636-2022</t>
+          <t>A 37004-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3366,10 +3356,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44818</v>
+        <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3381,14 +3371,19 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3397,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3406,10 +3401,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3418,46 +3413,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 39636-2022 artfynd.xlsx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 39636-2022 karta.png", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 39636-2022 georefererad karta.tif", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 39636-2022 FSC-klagomål.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 39636-2022 FSC-klagomål mail.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 39636-2022 tillsynsbegäran.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 39636-2022 tillsynsbegäran mail.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2722-2022</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3471,10 +3466,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44580</v>
+        <v>44796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3487,82 +3482,82 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37004-2022</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3576,10 +3571,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44806</v>
+        <v>45991</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3591,19 +3586,14 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3633,46 +3623,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3686,10 +3680,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3702,19 +3696,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3729,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3742,35 +3736,39 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
@@ -3794,7 +3792,7 @@
         <v>45259</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3882,7 +3880,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3896,10 +3894,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44966</v>
+        <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3912,16 +3910,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3936,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3952,46 +3950,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 41259-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4005,10 +3999,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45991</v>
+        <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4020,11 +4014,16 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -4051,56 +4050,20 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 41263-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4114,10 +4077,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46239</v>
+        <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4129,14 +4092,19 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4160,52 +4128,20 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41259-2022</t>
+          <t>A 45501-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4219,10 +4155,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44825</v>
+        <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4234,13 +4170,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4283,7 +4214,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41263-2022</t>
+          <t>A 45498-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4297,10 +4228,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44825</v>
+        <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4312,13 +4243,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4361,7 +4287,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45501-2022</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4375,10 +4301,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44845</v>
+        <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4390,8 +4316,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4434,7 +4365,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45498-2022</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4444,14 +4375,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44845</v>
+        <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4395,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4507,7 +4438,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4524,7 +4455,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4585,7 +4516,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4595,14 +4526,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44694</v>
+        <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4614,8 +4545,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4658,7 +4594,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4672,10 +4608,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44476</v>
+        <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,13 +4623,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4736,7 +4667,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4750,10 +4681,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44825</v>
+        <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4765,13 +4696,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4814,7 +4740,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4828,10 +4754,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44643</v>
+        <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,6 +4767,11 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -4887,7 +4818,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4901,10 +4832,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44761</v>
+        <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4916,8 +4847,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4960,7 +4896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4974,10 +4910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44806</v>
+        <v>45363</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4989,13 +4925,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5038,7 +4969,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5052,10 +4983,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45679</v>
+        <v>44643</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5068,7 +4999,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5128,7 +5059,7 @@
         <v>45209</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5221,7 +5152,7 @@
         <v>45070</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5277,7 +5208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5291,10 +5222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45121</v>
+        <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5306,8 +5237,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5350,7 +5286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5364,10 +5300,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5380,7 +5316,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5423,7 +5359,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5437,10 +5373,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45763</v>
+        <v>45936</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5453,7 +5389,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5496,7 +5432,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5510,10 +5446,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45796</v>
+        <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5525,8 +5461,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5569,7 +5510,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5583,10 +5524,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45279</v>
+        <v>45763</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5599,7 +5540,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5642,7 +5583,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5659,7 +5600,7 @@
         <v>45425</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5677,7 +5618,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5720,7 +5661,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5734,10 +5675,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5750,7 +5691,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5793,7 +5734,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5807,10 +5748,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45324</v>
+        <v>45439</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5822,13 +5763,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5871,7 +5807,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5885,10 +5821,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45418</v>
+        <v>45991</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5944,7 +5880,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5954,14 +5890,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45813</v>
+        <v>45333</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5973,8 +5909,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6017,7 +5958,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6031,10 +5972,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45089</v>
+        <v>45454</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6047,7 +5988,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6090,7 +6031,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6104,10 +6045,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45251</v>
+        <v>44526</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6120,7 +6061,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6163,7 +6104,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6177,10 +6118,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45425</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6192,13 +6133,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6241,7 +6177,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6255,10 +6191,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45775</v>
+        <v>45743</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6271,7 +6207,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6314,7 +6250,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6328,10 +6264,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45991</v>
+        <v>45775</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6344,7 +6280,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6387,7 +6323,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6401,10 +6337,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45302</v>
+        <v>45281</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6417,7 +6353,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6460,7 +6396,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6474,10 +6410,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45048</v>
+        <v>45302</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6490,7 +6426,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6533,7 +6469,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6547,10 +6483,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45763</v>
+        <v>45085</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6563,7 +6499,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6606,7 +6542,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6620,10 +6556,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46239</v>
+        <v>45251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6636,7 +6572,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6679,7 +6615,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6693,10 +6629,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>46171</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6709,7 +6645,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6752,7 +6688,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6766,10 +6702,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45425</v>
+        <v>46091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6781,13 +6717,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6830,7 +6761,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6844,10 +6775,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6860,7 +6791,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6903,7 +6834,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6917,10 +6848,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46091</v>
+        <v>46183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6933,7 +6864,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6976,7 +6907,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6986,14 +6917,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44643</v>
+        <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7006,7 +6937,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7049,7 +6980,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7063,10 +6994,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45740</v>
+        <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7078,8 +7009,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7122,7 +7058,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7136,10 +7072,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45351</v>
+        <v>45048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7149,11 +7085,6 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -7200,7 +7131,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7214,10 +7145,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45085</v>
+        <v>45089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7161,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7273,7 +7204,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7287,10 +7218,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45454</v>
+        <v>45679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7234,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7346,7 +7277,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7360,10 +7291,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45363</v>
+        <v>45418</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7307,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7419,7 +7350,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7433,10 +7364,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45936</v>
+        <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7449,7 +7380,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7492,7 +7423,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7506,10 +7437,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45839</v>
+        <v>45763</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7522,7 +7453,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7565,7 +7496,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7579,10 +7510,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45610</v>
+        <v>46239</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7638,7 +7569,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7652,10 +7583,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45333</v>
+        <v>45796</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7667,13 +7598,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7716,7 +7642,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7730,10 +7656,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>45279</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7672,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7789,7 +7715,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7799,14 +7725,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45743</v>
+        <v>45813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7745,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7862,7 +7788,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7876,10 +7802,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46171</v>
+        <v>45740</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7818,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7932,27 +7858,27 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="15" customHeight="1">
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>S 1718-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7891,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8004,152 +7930,6 @@
         <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>A 26886-2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>S 1718-2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E83" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59567-2025</t>
+          <t>A 17454-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45991</v>
+        <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,16 +2233,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>31.4</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -2269,9 +2269,140 @@
         <v>32</v>
       </c>
       <c r="U13" t="n">
+        <v>24</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Ullticka
+Barkticka
+Björksplintborre
+Blåmossa
+Blåsfliksmossa
+Granbarkgnagare
+Grön sköldmossa
+Grönpyrola
+Guldlockmossa
+Mindre märgborre
+Thomsons trägnagare
+Västlig hakmossa
+Blåsippa
+Glansfläck
+Skriftlav
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 59567-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32</v>
+      </c>
+      <c r="U14" t="n">
         <v>27</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Fjällig taggsvamp s.str.
@@ -2294,171 +2425,40 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17454-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>11</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>19</v>
-      </c>
-      <c r="T14" t="n">
-        <v>32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>24</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Ullticka
-Barkticka
-Björksplintborre
-Blåmossa
-Blåsfliksmossa
-Granbarkgnagare
-Grön sköldmossa
-Grönpyrola
-Guldlockmossa
-Mindre märgborre
-Thomsons trägnagare
-Västlig hakmossa
-Blåsippa
-Glansfläck
-Skriftlav
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2813,14 +2813,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -2866,155 +2866,155 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3506,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3522,42 +3522,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45991</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3627,46 +3627,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44966</v>
+        <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3736,46 +3736,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3805,20 +3805,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3845,35 +3845,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45324</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4847,13 +4847,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4896,7 +4891,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4910,10 +4905,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4921,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4969,7 +4964,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4983,10 +4978,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44643</v>
+        <v>45796</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4999,7 +4994,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5042,7 +5037,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45209</v>
+        <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5072,7 +5067,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5111,31 +5106,11 @@
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
-      <c r="Z43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5149,10 +5124,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45070</v>
+        <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5165,7 +5140,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5208,7 +5183,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5222,10 +5197,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45425</v>
+        <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5237,13 +5212,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5286,7 +5256,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5300,10 +5270,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5316,7 +5286,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5359,7 +5329,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5373,10 +5343,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45936</v>
+        <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5388,8 +5358,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5432,7 +5407,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5442,14 +5417,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45425</v>
+        <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5461,13 +5436,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5510,7 +5480,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5524,10 +5494,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45763</v>
+        <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5540,7 +5510,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5583,7 +5553,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5597,10 +5567,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5612,13 +5582,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5661,7 +5626,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5675,10 +5640,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45610</v>
+        <v>45839</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5691,7 +5656,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5734,7 +5699,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5748,10 +5713,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45439</v>
+        <v>45209</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5764,7 +5729,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5803,11 +5768,31 @@
         <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr"/>
+      <c r="Z52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5821,10 +5806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45991</v>
+        <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5837,7 +5822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5880,7 +5865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5894,10 +5879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45333</v>
+        <v>45121</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5909,13 +5894,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5958,7 +5938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5972,10 +5952,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45454</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5988,7 +5968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6031,7 +6011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6045,10 +6025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44526</v>
+        <v>45439</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6061,7 +6041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6104,7 +6084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6118,10 +6098,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45121</v>
+        <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6133,8 +6113,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6177,7 +6162,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6191,10 +6176,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45743</v>
+        <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6207,7 +6192,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6250,7 +6235,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6264,10 +6249,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45775</v>
+        <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6279,8 +6264,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6323,7 +6313,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6337,10 +6327,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45281</v>
+        <v>45740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6353,7 +6343,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6396,7 +6386,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6410,10 +6400,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45302</v>
+        <v>46183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6426,7 +6416,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6469,7 +6459,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6479,14 +6469,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45085</v>
+        <v>46185</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6499,7 +6489,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6542,7 +6532,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6556,10 +6546,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45251</v>
+        <v>45418</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6572,7 +6562,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6615,7 +6605,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6629,10 +6619,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46171</v>
+        <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6645,7 +6635,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6688,7 +6678,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6702,10 +6692,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46091</v>
+        <v>45775</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6718,7 +6708,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6761,7 +6751,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6775,10 +6765,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45610</v>
+        <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6791,7 +6781,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6834,7 +6824,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6848,10 +6838,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46183</v>
+        <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6907,7 +6897,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6917,14 +6907,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46185</v>
+        <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6937,7 +6927,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6980,7 +6970,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6994,10 +6984,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45351</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7009,13 +6999,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7058,7 +7043,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7072,10 +7057,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45048</v>
+        <v>46239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7088,7 +7073,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7131,7 +7116,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7145,10 +7130,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45089</v>
+        <v>45425</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7160,8 +7145,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7204,7 +7194,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7218,10 +7208,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45679</v>
+        <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7234,7 +7224,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7277,7 +7267,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7291,10 +7281,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45418</v>
+        <v>44643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7307,7 +7297,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7350,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7364,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44526</v>
+        <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7379,8 +7369,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7423,7 +7418,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7437,10 +7432,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45763</v>
+        <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7453,7 +7448,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7496,7 +7491,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7510,10 +7505,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46239</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7526,7 +7521,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7569,7 +7564,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7583,10 +7578,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45796</v>
+        <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7599,7 +7594,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7642,7 +7637,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7656,10 +7651,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45279</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7672,7 +7667,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7715,7 +7710,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7725,14 +7720,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45813</v>
+        <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7744,8 +7739,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45740</v>
+        <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>58</v>
       </c>
       <c r="T4" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="U4" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45796</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45839</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45209</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45121</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45439</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>46183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>46185</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45418</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45775</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>46239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45425</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45796</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45839</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45209</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45121</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45439</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>46183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>46185</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45418</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45089</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45775</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>46239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45425</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="U3" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2813,14 +2813,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -2866,155 +2866,155 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>45991</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3522,42 +3522,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3571,10 +3575,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3587,19 +3591,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3614,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3627,46 +3631,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45991</v>
+        <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3736,46 +3736,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3845,35 +3845,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4847,8 +4847,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4891,7 +4896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4905,10 +4910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4921,7 +4926,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4981,7 +4986,7 @@
         <v>45796</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5037,7 +5042,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44526</v>
+        <v>45279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5067,7 +5072,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5110,7 +5115,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5124,10 +5129,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45279</v>
+        <v>44643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5140,7 +5145,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5183,7 +5188,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5193,14 +5198,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46091</v>
+        <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5213,7 +5218,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5256,7 +5261,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45251</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5286,7 +5291,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5325,11 +5330,31 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
+      <c r="Z46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5343,10 +5368,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45425</v>
+        <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5358,13 +5383,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5407,7 +5427,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5417,14 +5437,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45813</v>
+        <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5437,7 +5457,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5480,7 +5500,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5494,10 +5514,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45991</v>
+        <v>45425</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5509,8 +5529,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5553,7 +5578,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5567,10 +5592,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45936</v>
+        <v>45991</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5583,7 +5608,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5626,7 +5651,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5640,10 +5665,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45839</v>
+        <v>46091</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5656,7 +5681,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5699,7 +5724,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5713,10 +5738,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45209</v>
+        <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5728,8 +5753,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5768,31 +5798,11 @@
         <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr"/>
-      <c r="Z52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5806,10 +5816,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45070</v>
+        <v>45763</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5822,7 +5832,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5865,7 +5875,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5879,10 +5889,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45121</v>
+        <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5894,8 +5904,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5938,7 +5953,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5952,10 +5967,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45439</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5968,7 +5983,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6011,7 +6026,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6025,10 +6040,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6041,7 +6056,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6084,7 +6099,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6098,10 +6113,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45425</v>
+        <v>45333</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6119,7 +6134,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6162,7 +6177,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6176,10 +6191,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46171</v>
+        <v>45454</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6192,7 +6207,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6235,7 +6250,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6249,10 +6264,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45324</v>
+        <v>44526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6264,13 +6279,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6313,7 +6323,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6327,10 +6337,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45740</v>
+        <v>45936</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6343,7 +6353,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6386,7 +6396,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6400,10 +6410,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46183</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6416,7 +6426,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6459,7 +6469,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6469,14 +6479,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46185</v>
+        <v>45121</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6489,7 +6499,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6532,7 +6542,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6546,10 +6556,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45418</v>
+        <v>45743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6562,7 +6572,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6605,7 +6615,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6619,10 +6629,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45089</v>
+        <v>45775</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6635,7 +6645,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6678,7 +6688,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6692,10 +6702,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45775</v>
+        <v>45281</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6708,7 +6718,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6768,7 +6778,7 @@
         <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6824,7 +6834,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6838,10 +6848,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>45085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6854,7 +6864,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6897,7 +6907,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6911,10 +6921,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>45251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6927,7 +6937,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6970,7 +6980,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6984,10 +6994,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>45610</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7000,7 +7010,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7043,7 +7053,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7057,10 +7067,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46239</v>
+        <v>46171</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7073,7 +7083,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7116,7 +7126,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7130,10 +7140,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45425</v>
+        <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7151,7 +7161,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7194,7 +7204,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7208,10 +7218,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44526</v>
+        <v>46183</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7224,7 +7234,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7267,7 +7277,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7277,14 +7287,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44643</v>
+        <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7297,7 +7307,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7340,7 +7350,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7354,10 +7364,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45351</v>
+        <v>45048</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7367,11 +7377,6 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -7418,7 +7423,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7432,10 +7437,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45085</v>
+        <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7448,7 +7453,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7491,7 +7496,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7505,10 +7510,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7521,7 +7526,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7564,7 +7569,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7578,10 +7583,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45363</v>
+        <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7594,7 +7599,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7637,7 +7642,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7651,10 +7656,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7667,7 +7672,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7710,7 +7715,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7724,10 +7729,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7739,13 +7744,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45743</v>
+        <v>46239</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="U3" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
@@ -1002,13 +1002,13 @@
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="U4" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1040,6 +1040,7 @@
 Björksplintborre
 Blomkålssvamp
 Blåmossa
+Brandticka
 Bronshjon
 Granbarkgnagare
 Grovticka
@@ -1129,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1287,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1425,7 +1426,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1565,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1699,7 @@
         <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1828,7 +1829,7 @@
         <v>44525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1958,7 +1959,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2091,7 +2092,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2220,7 +2221,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2351,7 +2352,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2482,7 +2483,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2601,7 +2602,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2711,7 +2712,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2803,7 +2804,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2813,14 +2814,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2833,13 +2834,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -2866,155 +2867,155 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -3038,7 +3039,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3149,7 +3150,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,7 +3255,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3360,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3452,7 +3453,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3466,10 +3467,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3482,7 +3483,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3522,46 +3523,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3575,10 +3572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3591,19 +3588,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3618,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3631,42 +3628,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3680,10 +3681,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44966</v>
+        <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3696,7 +3697,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3705,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3720,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3736,46 +3737,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3789,10 +3790,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3805,20 +3806,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3829,10 +3830,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3845,35 +3846,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3898,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4002,7 +4003,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4080,7 +4081,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4158,7 +4159,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4231,7 +4232,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4305,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4383,7 @@
         <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4455,7 +4456,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4534,7 @@
         <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4595,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4608,10 +4609,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4624,7 +4625,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4667,7 +4668,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4681,10 +4682,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4697,7 +4698,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4757,7 +4758,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4818,7 +4819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4832,10 +4833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45324</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4847,13 +4848,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4896,7 +4892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4910,10 +4906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4986,7 +4982,7 @@
         <v>45796</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5056,10 +5052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45279</v>
+        <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5072,7 +5068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5115,7 +5111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5129,10 +5125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44643</v>
+        <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5145,7 +5141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5205,7 +5201,7 @@
         <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5261,7 +5257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5275,10 +5271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5291,7 +5287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5330,31 +5326,11 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
-      <c r="Z46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5368,10 +5344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45070</v>
+        <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5384,7 +5360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5427,7 +5403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5441,10 +5417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45740</v>
+        <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5456,8 +5432,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5500,7 +5481,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5514,10 +5495,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45425</v>
+        <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5529,13 +5510,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5578,7 +5554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5592,10 +5568,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45991</v>
+        <v>46091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5608,7 +5584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5651,7 +5627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5665,10 +5641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46091</v>
+        <v>45209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5681,7 +5657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5720,11 +5696,31 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
+      <c r="Z51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5738,10 +5734,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45425</v>
+        <v>45070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5753,13 +5749,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5802,7 +5793,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5816,10 +5807,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45763</v>
+        <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5832,7 +5823,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5875,7 +5866,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5889,10 +5880,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45425</v>
+        <v>45439</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5904,13 +5895,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5953,7 +5939,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5967,10 +5953,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45439</v>
+        <v>45425</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5982,8 +5968,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6026,7 +6017,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6040,10 +6031,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45839</v>
+        <v>45936</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6056,7 +6047,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6099,7 +6090,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6113,10 +6104,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45333</v>
+        <v>45324</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6134,7 +6125,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6177,7 +6168,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6191,10 +6182,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45454</v>
+        <v>45839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6207,7 +6198,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6250,7 +6241,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6264,10 +6255,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44526</v>
+        <v>45418</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6280,7 +6271,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6323,7 +6314,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6337,10 +6328,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45936</v>
+        <v>45610</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6353,7 +6344,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6396,7 +6387,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6410,10 +6401,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>45089</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6426,7 +6417,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6469,7 +6460,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6483,10 +6474,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45121</v>
+        <v>45775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6499,7 +6490,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6542,7 +6533,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6556,10 +6547,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45743</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6572,7 +6563,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6615,7 +6606,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6629,10 +6620,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45775</v>
+        <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6645,7 +6636,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6688,7 +6679,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6702,10 +6693,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45281</v>
+        <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6718,7 +6709,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6761,7 +6752,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6771,14 +6762,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45302</v>
+        <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6791,7 +6782,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6834,7 +6825,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6848,10 +6839,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45085</v>
+        <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6864,7 +6855,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6907,7 +6898,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6921,10 +6912,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45251</v>
+        <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6937,7 +6928,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6980,7 +6971,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6994,10 +6985,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45610</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7010,7 +7001,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7053,7 +7044,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7067,10 +7058,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46171</v>
+        <v>45425</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7082,8 +7073,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7126,7 +7122,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7140,10 +7136,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45351</v>
+        <v>44526</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7155,13 +7151,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7204,7 +7195,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7218,10 +7209,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46183</v>
+        <v>44643</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7234,7 +7225,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7277,7 +7268,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7287,14 +7278,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46185</v>
+        <v>45351</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7306,8 +7297,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7350,7 +7346,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7364,10 +7360,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45048</v>
+        <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7380,7 +7376,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7423,7 +7419,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7437,10 +7433,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45089</v>
+        <v>45454</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7453,7 +7449,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7496,7 +7492,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7510,10 +7506,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45679</v>
+        <v>45363</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7526,7 +7522,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7569,7 +7565,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7583,10 +7579,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45418</v>
+        <v>46239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7599,7 +7595,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7642,7 +7638,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7656,10 +7652,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7672,7 +7668,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7715,7 +7711,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7729,10 +7725,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45763</v>
+        <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7744,8 +7740,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7788,7 +7789,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7802,10 +7803,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46239</v>
+        <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7818,7 +7819,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7878,7 +7879,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U4" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59566-2025</t>
+          <t>A 67894-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45991</v>
+        <v>44525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
         <v>9</v>
       </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1736,21 +1736,151 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>22</v>
       </c>
       <c r="T9" t="n">
+        <v>48</v>
+      </c>
+      <c r="U9" t="n">
+        <v>48</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Grönhjon
+Kortskaftad ärgspik
+Motaggsvamp
+Reliktbock
+Svartvit taggsvamp
+Tallticka
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blåmossa
+Bronshjon
+Granbarkgnagare
+Grovticka
+Grön sköldmossa
+Kornknutmossa
+Mindre märgborre
+Stor revmossa
+Stubbspretmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 59566-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
         <v>49</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>44</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Rotfingersvamp
@@ -1776,166 +1906,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67894-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44525</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>48</v>
-      </c>
-      <c r="U10" t="n">
-        <v>48</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Grönhjon
-Kortskaftad ärgspik
-Motaggsvamp
-Reliktbock
-Svartvit taggsvamp
-Tallticka
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blåmossa
-Bronshjon
-Granbarkgnagare
-Grovticka
-Grön sköldmossa
-Kornknutmossa
-Mindre märgborre
-Stor revmossa
-Stubbspretmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 21231-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46199</v>
+        <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -2977,156 +2977,156 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Spillkråka
+Trana</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 21231-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Spillkråka
-Trana</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
         <v/>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3523,42 +3523,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3572,10 +3576,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3592,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3597,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3612,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3628,46 +3632,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45991</v>
+        <v>44796</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3697,20 +3697,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3721,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3737,46 +3737,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3790,10 +3786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44796</v>
+        <v>45991</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3806,10 +3802,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3818,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3830,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3846,35 +3842,39 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4305,7 +4305,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44694</v>
+        <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4395,8 +4395,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4439,7 +4444,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4456,7 +4461,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4517,7 +4522,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4527,14 +4532,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44825</v>
+        <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4546,13 +4551,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44806</v>
+        <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>44806</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4848,8 +4848,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4892,7 +4897,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4906,10 +4911,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45763</v>
+        <v>45121</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4927,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4965,7 +4970,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4979,10 +4984,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45796</v>
+        <v>45363</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4995,7 +5000,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5038,7 +5043,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5055,7 +5060,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5068,7 +5073,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5111,7 +5116,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5125,10 +5130,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45279</v>
+        <v>45743</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5141,7 +5146,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5194,14 +5199,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45813</v>
+        <v>45763</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5214,7 +5219,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5271,10 +5276,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45740</v>
+        <v>45425</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5286,8 +5291,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5330,7 +5340,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5344,10 +5354,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45251</v>
+        <v>45775</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5360,7 +5370,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5403,7 +5413,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5417,10 +5427,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45425</v>
+        <v>45281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5432,13 +5442,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5481,7 +5486,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5495,10 +5500,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45991</v>
+        <v>45302</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5511,7 +5516,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5554,7 +5559,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46091</v>
+        <v>45085</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5584,7 +5589,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5627,7 +5632,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5641,10 +5646,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45209</v>
+        <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5657,7 +5662,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5696,31 +5701,11 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
-      <c r="Z51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5734,10 +5719,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45070</v>
+        <v>45610</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5750,7 +5735,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5793,7 +5778,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5807,10 +5792,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45121</v>
+        <v>45351</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5820,6 +5805,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -5866,7 +5856,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5880,10 +5870,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45439</v>
+        <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5896,7 +5886,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5939,7 +5929,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5956,7 +5946,7 @@
         <v>45425</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5974,7 +5964,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6017,7 +6007,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6031,10 +6021,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45936</v>
+        <v>45279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6047,7 +6037,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6090,7 +6080,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6104,10 +6094,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45324</v>
+        <v>44643</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6119,13 +6109,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6168,7 +6153,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6182,10 +6167,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45839</v>
+        <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6198,7 +6183,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6241,7 +6226,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6255,10 +6240,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45418</v>
+        <v>45089</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6271,7 +6256,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6314,7 +6299,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6328,10 +6313,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45610</v>
+        <v>45763</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6344,7 +6329,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6387,7 +6372,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6401,10 +6386,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45089</v>
+        <v>45209</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6417,7 +6402,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6456,11 +6441,31 @@
         <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr"/>
+      <c r="Z61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6474,10 +6479,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45775</v>
+        <v>45425</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6489,8 +6494,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6533,7 +6543,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6547,10 +6557,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45679</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6563,7 +6573,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6606,7 +6616,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6616,14 +6626,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45302</v>
+        <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6636,7 +6646,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6679,7 +6689,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6693,10 +6703,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46183</v>
+        <v>45439</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6709,7 +6719,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6752,7 +6762,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6762,14 +6772,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46185</v>
+        <v>45418</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6782,7 +6792,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6825,7 +6835,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6839,10 +6849,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>45333</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6854,8 +6864,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6898,7 +6913,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6912,10 +6927,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>45070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6928,7 +6943,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6971,7 +6986,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6985,10 +7000,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>45454</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7001,7 +7016,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7044,7 +7059,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7058,10 +7073,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45425</v>
+        <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7073,13 +7088,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7122,7 +7132,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7136,10 +7146,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44526</v>
+        <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7152,7 +7162,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7195,7 +7205,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7209,10 +7219,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44643</v>
+        <v>45991</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7225,7 +7235,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7268,7 +7278,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7282,10 +7292,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45351</v>
+        <v>46091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7297,13 +7307,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7346,7 +7351,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7360,10 +7365,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45085</v>
+        <v>45839</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7376,7 +7381,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7419,7 +7424,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7433,10 +7438,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45454</v>
+        <v>45936</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7449,7 +7454,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7492,7 +7497,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7506,10 +7511,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45363</v>
+        <v>45610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7522,7 +7527,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7565,7 +7570,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7579,10 +7584,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46239</v>
+        <v>46171</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7595,7 +7600,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7638,7 +7643,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7652,10 +7657,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>46183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7668,7 +7673,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7711,7 +7716,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7721,14 +7726,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>46185</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,13 +7745,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45743</v>
+        <v>46239</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7879,7 +7879,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>63</v>
       </c>
       <c r="T3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>45679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 67894-2021</t>
+          <t>A 59566-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44525</v>
+        <v>45991</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1736,21 +1736,151 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>22</v>
       </c>
       <c r="T9" t="n">
+        <v>49</v>
+      </c>
+      <c r="U9" t="n">
+        <v>44</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Rotfingersvamp
+Tallkötticka
+Talltita
+Ullticka
+Bronshjon
+Flagellkvastmossa
+Grön sköldmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Stubbspretmossa
+Thomsons trägnagare
+Vedticka
+Ekbräken
+Hultbräken
+Mattlummer
+Spillkråka
+Kungsfågel
+Kopparödla
+Skogsödla
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 67894-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44525</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
         <v>48</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>48</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Grönhjon
@@ -1776,166 +1906,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 59566-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>49</v>
-      </c>
-      <c r="U10" t="n">
-        <v>44</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Rotfingersvamp
-Tallkötticka
-Talltita
-Ullticka
-Bronshjon
-Flagellkvastmossa
-Grön sköldmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Stubbspretmossa
-Thomsons trägnagare
-Vedticka
-Ekbräken
-Hultbräken
-Mattlummer
-Spillkråka
-Kungsfågel
-Kopparödla
-Skogsödla
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
         <v>19</v>
       </c>
       <c r="T14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45679</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>44526</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 21231-2025</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45779</v>
+        <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -2977,156 +2977,156 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 21231-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
         <v>44818</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3523,46 +3523,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3576,10 +3572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3592,7 +3588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3601,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3616,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3632,42 +3628,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44796</v>
+        <v>45991</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3721,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3737,42 +3737,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3786,10 +3790,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45991</v>
+        <v>44796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3802,20 +3806,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3826,10 +3830,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3842,39 +3846,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
         <v>46239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4305,7 +4305,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44825</v>
+        <v>44694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4395,13 +4395,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4444,7 +4439,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4461,7 +4456,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4522,7 +4517,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4532,14 +4527,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44694</v>
+        <v>44825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4551,8 +4546,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4612,7 +4612,7 @@
         <v>44643</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44761</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45324</v>
+        <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44806</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4848,13 +4848,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4897,7 +4892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4911,10 +4906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45121</v>
+        <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4927,7 +4922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4970,7 +4965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4984,10 +4979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45363</v>
+        <v>44526</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5000,7 +4995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5043,7 +5038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5057,10 +5052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44526</v>
+        <v>45796</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5073,7 +5068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5116,7 +5111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5130,10 +5125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45743</v>
+        <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5146,7 +5141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5189,7 +5184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5203,10 +5198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45763</v>
+        <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5219,7 +5214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5262,7 +5257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5272,14 +5267,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45425</v>
+        <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5291,13 +5286,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5340,7 +5330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5354,10 +5344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45775</v>
+        <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5370,7 +5360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5413,7 +5403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5427,10 +5417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45281</v>
+        <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5442,8 +5432,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5486,7 +5481,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 59569-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5500,10 +5495,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45302</v>
+        <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5516,7 +5511,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5559,7 +5554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45085</v>
+        <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5589,7 +5584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5632,7 +5627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5646,10 +5641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5662,7 +5657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5705,7 +5700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5719,10 +5714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45610</v>
+        <v>45740</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5778,7 +5773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5792,10 +5787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45351</v>
+        <v>45209</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5807,13 +5802,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5852,11 +5842,31 @@
         <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
+      <c r="Z53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45796</v>
+        <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5886,7 +5896,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5929,7 +5939,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5943,10 +5953,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45425</v>
+        <v>45121</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5958,13 +5968,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6007,7 +6012,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6021,10 +6026,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45279</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6037,7 +6042,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6080,7 +6085,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6094,10 +6099,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44643</v>
+        <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6110,7 +6115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6153,7 +6158,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6167,10 +6172,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45048</v>
+        <v>45425</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6182,8 +6187,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6226,7 +6236,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6240,10 +6250,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45089</v>
+        <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6255,8 +6265,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6299,7 +6314,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6313,10 +6328,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45763</v>
+        <v>46171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6329,7 +6344,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6372,7 +6387,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6386,10 +6401,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45209</v>
+        <v>45418</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6402,7 +6417,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6441,31 +6456,11 @@
         <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr"/>
-      <c r="Z61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6479,10 +6474,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45425</v>
+        <v>45089</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6494,13 +6489,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6543,7 +6533,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6557,10 +6547,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45679</v>
+        <v>46183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6573,7 +6563,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6616,7 +6606,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6626,14 +6616,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45813</v>
+        <v>46185</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6646,7 +6636,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6689,7 +6679,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6703,10 +6693,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45439</v>
+        <v>45775</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6719,7 +6709,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6762,7 +6752,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6776,10 +6766,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45418</v>
+        <v>45302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6792,7 +6782,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6835,7 +6825,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6849,10 +6839,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45333</v>
+        <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6864,13 +6854,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6913,7 +6898,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6927,10 +6912,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45070</v>
+        <v>45763</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6943,7 +6928,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6986,7 +6971,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7000,10 +6985,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45454</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7016,7 +7001,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7059,7 +7044,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7073,10 +7058,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44526</v>
+        <v>45425</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7088,8 +7073,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7132,7 +7122,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7146,10 +7136,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45740</v>
+        <v>44526</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7162,7 +7152,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7205,7 +7195,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7219,10 +7209,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45991</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7235,7 +7225,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7278,7 +7268,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7292,10 +7282,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46091</v>
+        <v>44643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7308,7 +7298,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7351,7 +7341,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7365,10 +7355,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45839</v>
+        <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7380,8 +7370,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7424,7 +7419,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7438,10 +7433,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45936</v>
+        <v>45085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7454,7 +7449,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7497,7 +7492,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7511,10 +7506,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45610</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7527,7 +7522,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7570,7 +7565,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7584,10 +7579,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46171</v>
+        <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7600,7 +7595,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7643,7 +7638,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7657,10 +7652,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46183</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7673,7 +7668,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7716,7 +7711,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7726,14 +7721,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46185</v>
+        <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7745,8 +7740,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46239</v>
+        <v>45743</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7879,7 +7879,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE81"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 3152-2025</t>
+          <t>A 67868-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45679</v>
+        <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1439,16 +1439,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -1463,160 +1463,21 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="U7" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Apelsinticka
-Blå taggsvamp
-Dropptaggsvamp
-Grantaggsvamp
-Kandelabersvamp
-Koralltaggsvamp
-Orange taggsvamp
-Svartvit taggsvamp
-Talltita
-Ullticka
-Vedtrappmossa
-Vågticka
-Blomkålssvamp
-Blåmossa
-Grön sköldmossa
-Grönpyrola
-Mindre märgborre
-Plattlummer
-Rödgul trumpetsvamp
-Spindelblomster
-Vedticka
-Västlig hakmossa
-Mattlummer
-Vanlig padda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 3152-2025 artfynd.xlsx", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 3152-2025 karta.png", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 3152-2025 georefererad karta.tif", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 3152-2025 karta knärot.png", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 3152-2025 FSC-klagomål.docx", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 3152-2025 FSC-klagomål mail.docx", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 3152-2025 tillsynsbegäran.docx", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 3152-2025 tillsynsbegäran mail.docx", "A 3152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 3152-2025 prioriterade fågelarter.docx", "A 3152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 67868-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44525</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>26</v>
-      </c>
-      <c r="T8" t="n">
-        <v>67</v>
-      </c>
-      <c r="U8" t="n">
-        <v>67</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Grönhjon
@@ -1646,241 +1507,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67868-2021 artfynd.xlsx", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67868-2021 karta.png", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67868-2021 georefererad karta.tif", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67868-2021 FSC-klagomål.docx", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67868-2021 FSC-klagomål mail.docx", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67868-2021 tillsynsbegäran.docx", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67868-2021 tillsynsbegäran mail.docx", "A 67868-2021")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67868-2021 prioriterade fågelarter.docx", "A 67868-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 59566-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 67894-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="D8" s="1" t="n">
+        <v>44525</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>22</v>
       </c>
-      <c r="T9" t="n">
-        <v>49</v>
-      </c>
-      <c r="U9" t="n">
-        <v>44</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Rotfingersvamp
-Tallkötticka
-Talltita
-Ullticka
-Bronshjon
-Flagellkvastmossa
-Grön sköldmossa
-Grönpyrola
-Kornknutmossa
-Mindre märgborre
-Stubbspretmossa
-Thomsons trägnagare
-Vedticka
-Ekbräken
-Hultbräken
-Mattlummer
-Spillkråka
-Kungsfågel
-Kopparödla
-Skogsödla
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 67894-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44525</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="T8" t="n">
         <v>48</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U8" t="n">
         <v>48</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Grönhjon
@@ -1906,111 +1637,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 67894-2021 artfynd.xlsx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 67894-2021 karta.png", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 67894-2021 georefererad karta.tif", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 67894-2021 FSC-klagomål.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 67894-2021 FSC-klagomål mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 67894-2021 tillsynsbegäran.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 67894-2021 tillsynsbegäran mail.docx", "A 67894-2021")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 67894-2021 prioriterade fågelarter.docx", "A 67894-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 24801-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>7.1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K9" t="n">
         <v>10</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S9" t="n">
         <v>21</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T9" t="n">
         <v>43</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U9" t="n">
         <v>43</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blanksvart spiklav
@@ -2035,115 +1766,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 24801-2026 artfynd.xlsx", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 24801-2026 karta.png", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 24801-2026 georefererad karta.tif", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 24801-2026 karta knärot.png", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 24801-2026 FSC-klagomål.docx", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 24801-2026 FSC-klagomål mail.docx", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 24801-2026 tillsynsbegäran.docx", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 24801-2026 tillsynsbegäran mail.docx", "A 24801-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 24801-2026 prioriterade fågelarter.docx", "A 24801-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>S 2416-2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45469</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J10" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K10" t="n">
         <v>11</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>21</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T10" t="n">
         <v>46</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Barrviolspindling
 Dropptaggsvamp
@@ -2168,111 +1899,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/S 2416-2024 artfynd.xlsx", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/S 2416-2024 karta.png", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/S 2416-2024 georefererad karta.tif", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/S 2416-2024 FSC-klagomål.docx", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/S 2416-2024 FSC-klagomål mail.docx", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/S 2416-2024 tillsynsbegäran.docx", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/S 2416-2024 tillsynsbegäran mail.docx", "S 2416-2024")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/S 2416-2024 prioriterade fågelarter.docx", "S 2416-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 17454-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>46120</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>31.4</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K11" t="n">
         <v>11</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S11" t="n">
         <v>19</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T11" t="n">
         <v>32</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U11" t="n">
         <v>24</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -2295,115 +2026,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 59567-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S12" t="n">
         <v>19</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T12" t="n">
         <v>33</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U12" t="n">
         <v>28</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Fjällig taggsvamp s.str.
@@ -2426,115 +2157,237 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 59566-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24</v>
+      </c>
+      <c r="U13" t="n">
+        <v>22</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp
+Tallkötticka
+Talltita
+Ullticka
+Grön sköldmossa
+Grönpyrola
+Kornknutmossa
+Mindre märgborre
+Vedticka
+Ekbräken
+Hultbräken
+Spillkråka
+Kopparödla
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59566-2025 artfynd.xlsx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59566-2025 karta.png", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59566-2025 georefererad karta.tif", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59566-2025 FSC-klagomål.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59566-2025 FSC-klagomål mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59566-2025 tillsynsbegäran.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59566-2025 tillsynsbegäran mail.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59566-2025 prioriterade fågelarter.docx", "A 59566-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 3155-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>17.7</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>11</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T14" t="n">
         <v>16</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U14" t="n">
         <v>5</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Sårläka
@@ -2549,111 +2402,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 3155-2025 artfynd.xlsx", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 3155-2025 karta.png", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 3155-2025 georefererad karta.tif", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 3155-2025 FSC-klagomål.docx", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 3155-2025 FSC-klagomål mail.docx", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 3155-2025 tillsynsbegäran.docx", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 3155-2025 tillsynsbegäran mail.docx", "A 3155-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 3155-2025 prioriterade fågelarter.docx", "A 3155-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 68883-2021</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>44526</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S15" t="n">
         <v>6</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T15" t="n">
         <v>9</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kvällsmaskros
 Jungfrulin
@@ -2663,107 +2516,107 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 68883-2021 artfynd.xlsx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 68883-2021 karta.png", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 68883-2021 georefererad karta.tif", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 68883-2021 FSC-klagomål.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 68883-2021 FSC-klagomål mail.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 68883-2021 tillsynsbegäran.docx", "A 68883-2021")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 68883-2021 tillsynsbegäran mail.docx", "A 68883-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 47707-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.4</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T16" t="n">
         <v>10</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U16" t="n">
         <v>8</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Granbarkgnagare
@@ -2772,32 +2625,143 @@
 Vågbandad barkbock</t>
         </is>
       </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 47707-2023 artfynd.xlsx", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 47707-2023 karta.png", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 47707-2023 georefererad karta.tif", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 47707-2023 FSC-klagomål.docx", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 47707-2023 FSC-klagomål mail.docx", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 47707-2023 tillsynsbegäran.docx", "A 47707-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 47707-2023 tillsynsbegäran mail.docx", "A 47707-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 47707-2023 artfynd.xlsx", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 47707-2023 karta.png", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 47707-2023 georefererad karta.tif", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 47707-2023 FSC-klagomål.docx", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 47707-2023 FSC-klagomål mail.docx", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 47707-2023 tillsynsbegäran.docx", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 47707-2023 tillsynsbegäran mail.docx", "A 47707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -2821,7 +2785,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2911,7 +2875,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 21231-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2921,14 +2885,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46199</v>
+        <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2941,13 +2905,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -2977,163 +2941,157 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 21231-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39636-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44818</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 39636-2022 artfynd.xlsx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 39636-2022 karta.png", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 39636-2022 georefererad karta.tif", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 39636-2022 FSC-klagomål.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 39636-2022 FSC-klagomål mail.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 39636-2022 tillsynsbegäran.docx", "A 39636-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 39636-2022 tillsynsbegäran mail.docx", "A 39636-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39636-2022</t>
+          <t>A 2722-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3147,10 +3105,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44818</v>
+        <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3163,13 +3121,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -3178,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3187,58 +3145,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 39636-2022 artfynd.xlsx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 39636-2022 karta.png", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 39636-2022 georefererad karta.tif", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 39636-2022 FSC-klagomål.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 39636-2022 FSC-klagomål mail.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 39636-2022 tillsynsbegäran.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 39636-2022 tillsynsbegäran mail.docx", "A 39636-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2722-2022</t>
+          <t>A 37004-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3252,10 +3210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44580</v>
+        <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3267,8 +3225,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3301,49 +3264,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37004-2022</t>
+          <t>A 59570-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3357,10 +3320,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44806</v>
+        <v>45991</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3372,19 +3335,14 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3414,46 +3372,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3467,10 +3429,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3483,20 +3445,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3507,10 +3469,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3523,35 +3485,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3575,7 +3537,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3667,7 +3629,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3681,10 +3643,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3697,7 +3659,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3737,46 +3699,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3790,10 +3748,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44796</v>
+        <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3806,19 +3764,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3830,10 +3788,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3846,42 +3804,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 41259-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3895,10 +3853,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46239</v>
+        <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3910,14 +3868,19 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3941,52 +3904,20 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
+      <c r="V28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41259-2022</t>
+          <t>A 41263-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4003,7 +3934,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4021,7 +3952,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4064,7 +3995,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41263-2022</t>
+          <t>A 45501-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4078,10 +4009,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44825</v>
+        <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4093,13 +4024,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4142,7 +4068,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45501-2022</t>
+          <t>A 45498-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4159,7 +4085,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4172,7 +4098,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4215,7 +4141,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45498-2022</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4229,10 +4155,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44845</v>
+        <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4244,8 +4170,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4288,7 +4219,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4298,14 +4229,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44476</v>
+        <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4315,11 +4246,6 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4366,7 +4292,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4376,14 +4302,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44694</v>
+        <v>44476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4393,6 +4319,11 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -4439,7 +4370,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4453,10 +4384,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44476</v>
+        <v>44825</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4470,11 +4401,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4517,7 +4448,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4531,10 +4462,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44825</v>
+        <v>44643</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4546,13 +4477,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4595,7 +4521,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4609,10 +4535,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,7 +4551,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4668,7 +4594,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4682,10 +4608,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44761</v>
+        <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4697,8 +4623,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4741,7 +4672,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4755,10 +4686,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44806</v>
+        <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,11 +4703,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4819,7 +4750,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4833,10 +4764,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>45363</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4849,7 +4780,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4892,7 +4823,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4906,10 +4837,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45763</v>
+        <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4853,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4965,7 +4896,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4979,10 +4910,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44526</v>
+        <v>45209</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4995,7 +4926,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5034,6 +4965,26 @@
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
+      <c r="Z42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
@@ -5055,7 +5006,7 @@
         <v>45796</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5128,7 +5079,7 @@
         <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5184,7 +5135,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5198,10 +5149,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46091</v>
+        <v>45070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5214,7 +5165,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5274,7 +5225,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5330,7 +5281,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5344,10 +5295,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45251</v>
+        <v>46091</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5360,7 +5311,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5403,7 +5354,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5420,7 +5371,7 @@
         <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5438,7 +5389,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5498,7 +5449,7 @@
         <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5554,7 +5505,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5568,10 +5519,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45936</v>
+        <v>45839</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5584,7 +5535,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5627,7 +5578,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5641,10 +5592,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45839</v>
+        <v>45936</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5657,7 +5608,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5700,7 +5651,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5714,10 +5665,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45740</v>
+        <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5729,8 +5680,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5773,7 +5729,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5787,10 +5743,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45209</v>
+        <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5803,7 +5759,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5842,31 +5798,11 @@
         <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
-      <c r="Z53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5880,10 +5816,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45070</v>
+        <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5896,7 +5832,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5939,7 +5875,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5953,10 +5889,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45121</v>
+        <v>45763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5969,7 +5905,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6012,7 +5948,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6026,10 +5962,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45425</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6041,8 +5977,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6102,7 +6043,7 @@
         <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6158,7 +6099,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6172,10 +6113,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45425</v>
+        <v>45333</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6193,7 +6134,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6236,7 +6177,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6250,10 +6191,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45324</v>
+        <v>45454</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6265,13 +6206,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6314,7 +6250,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6328,10 +6264,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46171</v>
+        <v>44526</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6344,7 +6280,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6387,7 +6323,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6401,10 +6337,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45418</v>
+        <v>46171</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6417,7 +6353,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6460,7 +6396,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6474,10 +6410,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45089</v>
+        <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6490,7 +6426,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6533,7 +6469,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6543,14 +6479,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6563,7 +6499,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6606,7 +6542,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6616,14 +6552,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46185</v>
+        <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6636,7 +6572,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6679,7 +6615,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6693,10 +6629,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45775</v>
+        <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6709,7 +6645,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6752,7 +6688,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6766,10 +6702,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45302</v>
+        <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6782,7 +6718,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6825,7 +6761,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6839,10 +6775,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6855,7 +6791,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6898,7 +6834,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6912,10 +6848,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6928,7 +6864,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6971,7 +6907,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6985,10 +6921,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7001,7 +6937,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7044,7 +6980,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7058,10 +6994,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45425</v>
+        <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7073,13 +7009,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7122,7 +7053,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7136,10 +7067,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7152,7 +7083,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7195,7 +7126,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7209,10 +7140,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>45351</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7224,8 +7155,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7268,7 +7204,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7282,10 +7218,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44643</v>
+        <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7298,7 +7234,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7341,7 +7277,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7355,10 +7291,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45351</v>
+        <v>46239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7370,13 +7306,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7419,7 +7350,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7433,10 +7364,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45085</v>
+        <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7449,7 +7380,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7492,7 +7423,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7506,10 +7437,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7522,7 +7453,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7565,7 +7496,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7579,10 +7510,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45363</v>
+        <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7595,7 +7526,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7638,7 +7569,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7652,10 +7583,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7668,7 +7599,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7711,7 +7642,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7725,10 +7656,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,13 +7671,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7786,27 +7712,27 @@
       </c>
       <c r="V79" s="2" t="inlineStr"/>
     </row>
-    <row r="80" ht="15" customHeight="1">
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>S 1718-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45743</v>
+        <v>46188</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7745,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7858,79 +7784,6 @@
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>S 1718-2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45991</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44825</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>44643</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>44761</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45363</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45209</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45796</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>46091</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45839</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>45936</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45425</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45333</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45454</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44526</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>46171</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45351</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>46188</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45991</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44825</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>44845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44825</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>44643</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>44761</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45363</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45209</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45796</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>46091</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45425</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45839</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>45936</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45425</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45333</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45454</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44526</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>46171</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45351</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>46239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>46188</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AE78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="U3" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
 Knärot
 Lakritsmusseron
 Rotfingersvamp
+Skrovlig taggsvamp
 Apelsinticka
 Blå taggsvamp
 Brunlångöra
@@ -856,6 +857,7 @@
 Orange taggsvamp
 Skarp dropptaggsvamp
 Svartvit taggsvamp
+Tallkötticka
 Tallticka
 Talltita
 Ullticka
@@ -959,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1005,10 +1007,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="U4" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1130,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1288,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1560,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1823,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1952,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2083,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2214,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2336,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2455,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2565,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2657,7 +2659,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2667,14 +2669,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2687,13 +2689,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2720,155 +2722,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -2892,7 +2894,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3003,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3108,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3213,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3306,7 +3308,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59570-2025</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3320,10 +3322,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45991</v>
+        <v>45259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3336,7 +3338,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3376,46 +3378,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59570-2025 artfynd.xlsx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59570-2025 karta.png", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59570-2025 georefererad karta.tif", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59570-2025 FSC-klagomål.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59570-2025 FSC-klagomål mail.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59570-2025 tillsynsbegäran.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59570-2025 tillsynsbegäran mail.docx", "A 59570-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59570-2025 prioriterade fågelarter.docx", "A 59570-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3429,10 +3427,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3445,19 +3443,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3472,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3485,42 +3483,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3534,10 +3536,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3550,19 +3552,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3577,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3590,46 +3592,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3643,10 +3641,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,13 +3657,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3699,42 +3697,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 41259-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3748,10 +3746,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46239</v>
+        <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3763,14 +3761,19 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3794,52 +3797,20 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
-        <v/>
-      </c>
+      <c r="V27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41259-2022</t>
+          <t>A 41263-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3856,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3874,7 +3845,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3917,7 +3888,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41263-2022</t>
+          <t>A 45501-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3931,10 +3902,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44825</v>
+        <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,13 +3917,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3995,7 +3961,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45501-2022</t>
+          <t>A 45498-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4012,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4025,7 +3991,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4068,7 +4034,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45498-2022</t>
+          <t>A 55853-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4082,10 +4048,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44845</v>
+        <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4097,8 +4063,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4141,7 +4112,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4151,14 +4122,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44476</v>
+        <v>44694</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,11 +4139,6 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -4219,7 +4185,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 55861-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4229,14 +4195,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44694</v>
+        <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4246,6 +4212,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4292,7 +4263,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4306,10 +4277,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44476</v>
+        <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4323,11 +4294,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4370,7 +4341,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4384,10 +4355,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44825</v>
+        <v>44643</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4399,13 +4370,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4448,7 +4414,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4462,10 +4428,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4478,7 +4444,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4521,7 +4487,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4535,10 +4501,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44761</v>
+        <v>44806</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4550,8 +4516,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4594,7 +4565,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4608,10 +4579,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44806</v>
+        <v>45679</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4623,13 +4594,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4672,7 +4638,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4686,10 +4652,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45324</v>
+        <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,13 +4667,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4750,7 +4711,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4764,10 +4725,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45363</v>
+        <v>44526</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4780,7 +4741,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4823,7 +4784,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4833,14 +4794,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44643</v>
+        <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4853,7 +4814,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4896,7 +4857,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4910,10 +4871,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45209</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4926,7 +4887,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4965,31 +4926,11 @@
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
-      <c r="Z42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5003,10 +4944,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45796</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5019,7 +4960,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5062,7 +5003,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5076,10 +5017,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45279</v>
+        <v>45425</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5091,8 +5032,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5135,7 +5081,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5149,10 +5095,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45070</v>
+        <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5165,7 +5111,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5208,7 +5154,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5218,14 +5164,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45813</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5238,7 +5184,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5277,11 +5223,31 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
+      <c r="Z46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5295,10 +5261,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46091</v>
+        <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5311,7 +5277,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5354,7 +5320,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5368,10 +5334,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45425</v>
+        <v>45121</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5383,13 +5349,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5432,7 +5393,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59569-2025</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5446,10 +5407,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45991</v>
+        <v>45439</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5462,7 +5423,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5505,7 +5466,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5519,10 +5480,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45839</v>
+        <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5535,7 +5496,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5578,7 +5539,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5592,10 +5553,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45936</v>
+        <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5607,8 +5568,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5651,7 +5617,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5665,10 +5631,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45425</v>
+        <v>45324</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5686,7 +5652,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5729,7 +5695,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5743,10 +5709,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45740</v>
+        <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5759,7 +5725,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5819,7 +5785,7 @@
         <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5875,7 +5841,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5889,10 +5855,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45763</v>
+        <v>45418</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5905,7 +5871,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5948,7 +5914,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5962,10 +5928,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45425</v>
+        <v>45089</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5977,13 +5943,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6026,7 +5987,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6040,10 +6001,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45439</v>
+        <v>46171</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6056,7 +6017,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6099,7 +6060,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6113,10 +6074,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45333</v>
+        <v>45775</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6128,13 +6089,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6177,7 +6133,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6191,10 +6147,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45454</v>
+        <v>46183</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6207,7 +6163,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6250,7 +6206,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6260,14 +6216,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44526</v>
+        <v>46185</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6280,7 +6236,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6323,7 +6279,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6337,10 +6293,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46171</v>
+        <v>45302</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6353,7 +6309,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6396,7 +6352,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6410,10 +6366,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46183</v>
+        <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6469,7 +6425,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6479,14 +6435,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46185</v>
+        <v>45763</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6499,7 +6455,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6542,7 +6498,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6556,10 +6512,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45121</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6572,7 +6528,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6615,7 +6571,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6629,10 +6585,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>45425</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6644,8 +6600,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6688,7 +6649,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6702,10 +6663,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45775</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6718,7 +6679,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6761,7 +6722,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6775,10 +6736,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6791,7 +6752,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6834,7 +6795,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6848,10 +6809,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45302</v>
+        <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6863,8 +6824,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6924,7 +6890,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6980,7 +6946,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6994,10 +6960,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45251</v>
+        <v>45454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7010,7 +6976,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7053,7 +7019,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7067,10 +7033,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>45363</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7083,7 +7049,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7126,7 +7092,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7140,10 +7106,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45351</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7155,13 +7121,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7204,7 +7165,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7218,10 +7179,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45048</v>
+        <v>45610</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7234,7 +7195,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7277,7 +7238,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7291,10 +7252,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46239</v>
+        <v>45333</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7306,8 +7267,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7350,7 +7316,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7364,10 +7330,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45089</v>
+        <v>45743</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7380,7 +7346,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7423,7 +7389,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7437,10 +7403,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45679</v>
+        <v>45796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7453,7 +7419,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7496,7 +7462,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7510,10 +7476,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45418</v>
+        <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7526,7 +7492,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7566,27 +7532,27 @@
       </c>
       <c r="V77" s="2" t="inlineStr"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>S 1718-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44526</v>
+        <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7599,7 +7565,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7638,152 +7604,6 @@
         <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A 18491-2025</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>S 1718-2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2722,155 +2722,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3338,20 +3338,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3378,35 +3378,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3592,35 +3592,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>44694</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44643</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>44761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44806</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4594,8 +4594,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4638,7 +4643,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4652,10 +4657,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4668,7 +4673,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4711,7 +4716,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4725,10 +4730,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44526</v>
+        <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4741,7 +4746,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4784,7 +4789,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4794,14 +4799,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45813</v>
+        <v>45209</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4814,7 +4819,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4853,11 +4858,31 @@
         <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr"/>
+      <c r="Z41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4871,10 +4896,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>45070</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4887,7 +4912,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4930,7 +4955,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4940,14 +4965,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>45813</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4960,7 +4985,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5003,7 +5028,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5017,10 +5042,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45425</v>
+        <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5032,13 +5057,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5081,7 +5101,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5095,10 +5115,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46091</v>
+        <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5110,8 +5130,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5154,7 +5179,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5168,10 +5193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5184,7 +5209,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5223,31 +5248,11 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
-      <c r="Z46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45070</v>
+        <v>45839</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45121</v>
+        <v>45936</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45439</v>
+        <v>45610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45936</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5553,10 +5558,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45425</v>
+        <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5568,13 +5573,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5627,14 +5627,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45324</v>
+        <v>46185</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5646,13 +5646,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5695,7 +5690,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45839</v>
+        <v>45425</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5724,8 +5719,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>45763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5841,7 +5841,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45418</v>
+        <v>45425</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5870,8 +5870,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5914,7 +5919,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5928,10 +5933,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45089</v>
+        <v>45439</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5944,7 +5949,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5987,7 +5992,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6001,10 +6006,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46171</v>
+        <v>45333</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6016,8 +6021,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6060,7 +6070,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6074,10 +6084,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45775</v>
+        <v>45454</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6090,7 +6100,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6133,7 +6143,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6147,10 +6157,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46183</v>
+        <v>44526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6163,7 +6173,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6206,7 +6216,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6216,14 +6226,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46185</v>
+        <v>45121</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6236,7 +6246,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6279,7 +6289,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6293,10 +6303,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45302</v>
+        <v>45743</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6309,7 +6319,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6352,7 +6362,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6366,10 +6376,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45048</v>
+        <v>45775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6382,7 +6392,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6425,7 +6435,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6439,10 +6449,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45763</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6455,7 +6465,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6498,7 +6508,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6512,10 +6522,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6528,7 +6538,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6571,7 +6581,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6585,10 +6595,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45425</v>
+        <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6600,13 +6610,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6649,7 +6654,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6663,10 +6668,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44526</v>
+        <v>45251</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6679,7 +6684,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6722,7 +6727,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6736,10 +6741,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44643</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6752,7 +6757,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6795,7 +6800,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6809,10 +6814,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45351</v>
+        <v>46239</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6824,13 +6829,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45085</v>
+        <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6902,8 +6902,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6946,7 +6951,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45454</v>
+        <v>45048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6976,7 +6981,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7019,7 +7024,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7033,10 +7038,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45363</v>
+        <v>45089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7049,7 +7054,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7092,7 +7097,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7106,10 +7111,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>45679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7122,7 +7127,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7165,7 +7170,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7179,10 +7184,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45610</v>
+        <v>45418</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7195,7 +7200,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7238,7 +7243,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7252,10 +7257,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45333</v>
+        <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7267,13 +7272,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45743</v>
+        <v>45763</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
         <v>45796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE78"/>
+  <dimension ref="A1:AE76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="U3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17454-2026</t>
+          <t>A 59567-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46120</v>
+        <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1967,16 +1967,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>31.4</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -2000,12 +2000,143 @@
         <v>19</v>
       </c>
       <c r="T11" t="n">
+        <v>33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>28</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Fjällig taggsvamp s.str.
+Kandelabersvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vintertagging
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Brandticka
+Grovticka
+Grön sköldmossa
+Jättesvampmal
+Mindre märgborre
+Vågbandad barkbock
+Spillkråka
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17454-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19</v>
+      </c>
+      <c r="T12" t="n">
         <v>32</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>24</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -2028,171 +2159,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 59567-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>19</v>
-      </c>
-      <c r="T12" t="n">
-        <v>33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>28</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Fjällig taggsvamp s.str.
-Kandelabersvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vintertagging
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Brandticka
-Grovticka
-Grön sköldmossa
-Jättesvampmal
-Mindre märgborre
-Vågbandad barkbock
-Spillkråka
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
         <v/>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 21231-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46199</v>
+        <v>45779</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2725,263 +2725,263 @@
         <v>3</v>
       </c>
       <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Spillkråka
+Trana</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 21231-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Spillkråka
-Trana</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
         <v/>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3483,46 +3483,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3536,10 +3532,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,7 +3548,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3561,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3576,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3592,35 +3588,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55853-2021</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44476</v>
+        <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4061,11 +4061,6 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -4112,7 +4107,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4122,14 +4117,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44694</v>
+        <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4141,8 +4136,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55861-2021</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44476</v>
+        <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4214,13 +4214,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4263,7 +4258,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4277,10 +4272,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44825</v>
+        <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4292,13 +4287,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4341,7 +4331,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4355,10 +4345,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44643</v>
+        <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4368,6 +4358,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -4414,7 +4409,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44761</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4444,7 +4439,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4487,7 +4482,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4501,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44806</v>
+        <v>45333</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4518,11 +4513,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4565,7 +4560,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4579,10 +4574,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45324</v>
+        <v>45209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4594,13 +4589,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4639,11 +4629,31 @@
         <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
+      <c r="Z38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4657,10 +4667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45363</v>
+        <v>45743</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4673,7 +4683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4716,7 +4726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44643</v>
+        <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4746,7 +4756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4789,7 +4799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4803,10 +4813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45209</v>
+        <v>45121</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4858,31 +4868,11 @@
         <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr"/>
-      <c r="Z41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4896,10 +4886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45070</v>
+        <v>45439</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4912,7 +4902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4955,7 +4945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4965,14 +4955,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45813</v>
+        <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4985,7 +4975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5028,7 +5018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5042,10 +5032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46091</v>
+        <v>45796</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5058,7 +5048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5101,7 +5091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5115,10 +5105,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45425</v>
+        <v>45279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5130,13 +5120,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5179,7 +5164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5189,14 +5174,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45740</v>
+        <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5209,7 +5194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5252,7 +5237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5266,10 +5251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45839</v>
+        <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5281,8 +5266,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5325,7 +5315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45936</v>
+        <v>45324</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5354,8 +5344,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45610</v>
+        <v>44526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5428,7 +5423,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46171</v>
+        <v>45418</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5558,10 +5553,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46183</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5574,7 +5569,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5617,7 +5612,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5627,14 +5622,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46185</v>
+        <v>45740</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,7 +5642,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5690,7 +5685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45425</v>
+        <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5719,13 +5714,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5768,7 +5758,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5782,10 +5772,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45763</v>
+        <v>45251</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5798,7 +5788,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5841,7 +5831,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5858,7 +5848,7 @@
         <v>45425</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5876,7 +5866,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5919,7 +5909,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5933,10 +5923,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45439</v>
+        <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5949,7 +5939,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5992,7 +5982,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6006,10 +5996,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45333</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6021,13 +6011,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6070,7 +6055,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6084,10 +6069,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45454</v>
+        <v>45302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6100,7 +6085,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6143,7 +6128,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6157,10 +6142,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44526</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6173,7 +6158,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6216,7 +6201,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6230,10 +6215,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45121</v>
+        <v>45048</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6274,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6303,10 +6288,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45743</v>
+        <v>45763</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6319,7 +6304,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6362,7 +6347,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6376,10 +6361,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45775</v>
+        <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6392,7 +6377,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6435,7 +6420,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6445,14 +6430,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6465,7 +6450,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6508,7 +6493,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6522,10 +6507,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45302</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6538,7 +6523,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6581,7 +6566,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6595,10 +6580,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45085</v>
+        <v>45425</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6610,8 +6595,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6654,7 +6644,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6668,10 +6658,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45251</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6684,7 +6674,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6727,7 +6717,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6741,10 +6731,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6757,7 +6747,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6800,7 +6790,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6814,10 +6804,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46239</v>
+        <v>44643</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6830,7 +6820,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6890,7 +6880,7 @@
         <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6951,7 +6941,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6965,10 +6955,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45048</v>
+        <v>45085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6981,7 +6971,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7024,7 +7014,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7038,10 +7028,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45089</v>
+        <v>45454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7054,7 +7044,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7097,7 +7087,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7111,10 +7101,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45679</v>
+        <v>45363</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7127,7 +7117,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7170,7 +7160,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7184,10 +7174,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45418</v>
+        <v>45936</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7200,7 +7190,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7243,7 +7233,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7257,10 +7247,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7273,7 +7263,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7316,7 +7306,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7330,10 +7320,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45763</v>
+        <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7346,7 +7336,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7386,27 +7376,27 @@
       </c>
       <c r="V75" s="2" t="inlineStr"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>S 1718-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45796</v>
+        <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7419,7 +7409,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7458,152 +7448,6 @@
         <v>0</v>
       </c>
       <c r="V76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>A 64075-2023</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>S 1718-2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="U3" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59567-2025</t>
+          <t>A 17454-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45991</v>
+        <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1967,16 +1967,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>31.4</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -2000,12 +2000,143 @@
         <v>19</v>
       </c>
       <c r="T11" t="n">
+        <v>32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Ullticka
+Barkticka
+Björksplintborre
+Blåmossa
+Blåsfliksmossa
+Granbarkgnagare
+Grön sköldmossa
+Grönpyrola
+Guldlockmossa
+Mindre märgborre
+Thomsons trägnagare
+Västlig hakmossa
+Blåsippa
+Glansfläck
+Skriftlav
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 59567-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19</v>
+      </c>
+      <c r="T12" t="n">
         <v>33</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>28</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Fjällig taggsvamp s.str.
@@ -2028,171 +2159,40 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 17454-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>19</v>
-      </c>
-      <c r="T12" t="n">
-        <v>32</v>
-      </c>
-      <c r="U12" t="n">
-        <v>24</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Motaggsvamp
-Ullticka
-Barkticka
-Björksplintborre
-Blåmossa
-Blåsfliksmossa
-Granbarkgnagare
-Grön sköldmossa
-Grönpyrola
-Guldlockmossa
-Mindre märgborre
-Thomsons trägnagare
-Västlig hakmossa
-Blåsippa
-Glansfläck
-Skriftlav
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
         <v/>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21231-2025</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45779</v>
+        <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2725,263 +2725,263 @@
         <v>3</v>
       </c>
       <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 21231-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3483,42 +3483,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3532,10 +3536,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3548,7 +3552,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3557,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3572,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3588,39 +3592,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,8 +4438,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4482,7 +4487,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4501,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45333</v>
+        <v>45363</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4511,13 +4516,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45209</v>
+        <v>44643</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4629,31 +4629,11 @@
         <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
-      <c r="Z38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4667,10 +4647,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45743</v>
+        <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4683,7 +4663,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4722,6 +4702,26 @@
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -4743,7 +4743,7 @@
         <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45121</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45439</v>
+        <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4901,8 +4901,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4945,7 +4950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4959,10 +4964,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45763</v>
+        <v>46091</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5018,7 +5023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5032,10 +5037,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45796</v>
+        <v>45425</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5047,8 +5052,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5091,7 +5101,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45279</v>
+        <v>45763</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5121,7 +5131,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5164,7 +5174,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5174,14 +5184,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45813</v>
+        <v>45425</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5193,8 +5203,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5237,7 +5252,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5251,10 +5266,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45425</v>
+        <v>45439</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5266,13 +5281,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5315,7 +5325,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5329,10 +5339,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45324</v>
+        <v>45333</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5350,7 +5360,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5393,7 +5403,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5407,10 +5417,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44526</v>
+        <v>45839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5423,7 +5433,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5466,7 +5476,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5480,10 +5490,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45418</v>
+        <v>45454</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5496,7 +5506,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5539,7 +5549,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5553,10 +5563,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>44526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5569,7 +5579,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5612,7 +5622,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5626,10 +5636,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45740</v>
+        <v>45936</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5642,7 +5652,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5685,7 +5695,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5699,10 +5709,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45839</v>
+        <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5715,7 +5725,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5758,7 +5768,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5772,10 +5782,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45251</v>
+        <v>45743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5788,7 +5798,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5831,7 +5841,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5845,10 +5855,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45425</v>
+        <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5860,13 +5870,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5909,7 +5914,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5923,10 +5928,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45775</v>
+        <v>45281</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5939,7 +5944,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6072,7 +6077,7 @@
         <v>45302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6128,7 +6133,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6142,10 +6147,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45085</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6158,7 +6163,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6201,7 +6206,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6215,10 +6220,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45048</v>
+        <v>45251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6231,7 +6236,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6274,7 +6279,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6288,10 +6293,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45763</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6304,7 +6309,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6347,7 +6352,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6361,10 +6366,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46183</v>
+        <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6374,6 +6379,11 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -6420,7 +6430,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6430,14 +6440,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6450,7 +6460,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6493,7 +6503,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6507,10 +6517,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>46183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6523,7 +6533,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6566,7 +6576,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6576,14 +6586,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45425</v>
+        <v>46185</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6595,13 +6605,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44526</v>
+        <v>45048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6674,7 +6679,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6717,7 +6722,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6731,10 +6736,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46091</v>
+        <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6747,7 +6752,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6790,7 +6795,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6804,10 +6809,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44643</v>
+        <v>45679</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6820,7 +6825,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6863,7 +6868,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6877,10 +6882,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45351</v>
+        <v>45418</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6892,13 +6897,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6941,7 +6941,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45085</v>
+        <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45454</v>
+        <v>45763</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45363</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7160,7 +7160,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45936</v>
+        <v>45796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45610</v>
+        <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7306,7 +7306,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7316,14 +7316,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46239</v>
+        <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="U3" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,6 @@
 Knärot
 Lakritsmusseron
 Rotfingersvamp
-Skrovlig taggsvamp
 Apelsinticka
 Blå taggsvamp
 Brunlångöra
@@ -961,7 +960,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1007,10 +1006,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="U4" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1131,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1289,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1427,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1561,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1691,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1824,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1953,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2084,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2215,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2337,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2456,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2566,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2658,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 21231-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2668,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46199</v>
+        <v>45779</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2688,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2725,263 +2724,263 @@
         <v>3</v>
       </c>
       <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Spillkråka
+Trana</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 21231-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Spillkråka
-Trana</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
         <v/>
       </c>
     </row>
@@ -3005,7 +3004,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3093,7 +3092,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2722-2022</t>
+          <t>A 37004-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3107,10 +3106,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44580</v>
+        <v>44806</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3122,8 +3121,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3156,49 +3160,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37004-2022</t>
+          <t>A 2722-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3212,10 +3216,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44806</v>
+        <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3227,13 +3231,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3266,42 +3265,42 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
     </row>
@@ -3325,7 +3324,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3412,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3443,7 +3442,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3452,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3467,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3483,46 +3482,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3536,10 +3531,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,7 +3547,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3561,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3576,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3592,35 +3587,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3643,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3748,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3826,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3904,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3977,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4034,7 +4033,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4044,14 +4043,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44694</v>
+        <v>44643</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4063,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4107,7 +4106,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4121,10 +4120,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44825</v>
+        <v>44761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,13 +4135,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4185,7 +4179,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4195,14 +4189,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44643</v>
+        <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4209,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4258,7 +4252,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4272,10 +4266,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44761</v>
+        <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4287,8 +4281,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4348,7 +4347,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4409,7 +4408,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4423,10 +4422,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45324</v>
+        <v>45439</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,13 +4437,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4487,7 +4481,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4501,10 +4495,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45363</v>
+        <v>45085</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4517,7 +4511,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4560,7 +4554,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4574,10 +4568,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44643</v>
+        <v>45454</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4590,7 +4584,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4633,7 +4627,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4647,10 +4641,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45209</v>
+        <v>45363</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,7 +4657,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4702,31 +4696,11 @@
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
-      <c r="Z39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4740,10 +4714,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45070</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4756,7 +4730,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4799,7 +4773,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4813,10 +4787,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4829,7 +4803,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4889,7 +4863,7 @@
         <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4950,7 +4924,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4964,10 +4938,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46091</v>
+        <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4979,8 +4953,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5023,7 +5002,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5037,10 +5016,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45425</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5052,13 +5031,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5101,7 +5075,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5115,10 +5089,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45763</v>
+        <v>44526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5131,7 +5105,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5174,7 +5148,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5188,10 +5162,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45425</v>
+        <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5209,7 +5183,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5252,7 +5226,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5266,10 +5240,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45439</v>
+        <v>45743</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5282,7 +5256,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5325,7 +5299,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5339,10 +5313,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45333</v>
+        <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5354,13 +5328,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5403,7 +5372,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5417,10 +5386,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45839</v>
+        <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5433,7 +5402,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5476,7 +5445,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5490,10 +5459,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45454</v>
+        <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5506,7 +5475,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5549,7 +5518,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5563,10 +5532,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44526</v>
+        <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5579,7 +5548,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5622,7 +5591,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5636,10 +5605,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45936</v>
+        <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5652,7 +5621,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5695,7 +5664,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5705,14 +5674,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45121</v>
+        <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5725,7 +5694,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5768,7 +5737,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5782,10 +5751,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45743</v>
+        <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5797,8 +5766,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5858,7 +5832,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5914,7 +5888,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5928,10 +5902,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45281</v>
+        <v>45302</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5944,7 +5918,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5987,7 +5961,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6001,10 +5975,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>45740</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6017,7 +5991,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6060,7 +6034,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6074,10 +6048,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45302</v>
+        <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6090,7 +6064,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6133,7 +6107,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6147,10 +6121,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45085</v>
+        <v>45763</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6163,7 +6137,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6206,7 +6180,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6220,10 +6194,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45251</v>
+        <v>45209</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6236,7 +6210,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6275,11 +6249,31 @@
         <v>0</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
+      <c r="Z60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6293,10 +6287,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>45070</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6309,7 +6303,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6352,7 +6346,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6366,10 +6360,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45351</v>
+        <v>45121</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6379,11 +6373,6 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -6430,7 +6419,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6444,10 +6433,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6460,7 +6449,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6503,7 +6492,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6517,10 +6506,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46183</v>
+        <v>45425</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6532,8 +6521,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6576,7 +6570,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6586,14 +6580,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46185</v>
+        <v>44526</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6606,7 +6600,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6649,7 +6643,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6663,10 +6657,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45048</v>
+        <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6679,7 +6673,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6722,7 +6716,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6736,10 +6730,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45089</v>
+        <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6752,7 +6746,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6795,7 +6789,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6809,10 +6803,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45679</v>
+        <v>45839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6825,7 +6819,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6868,7 +6862,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6882,10 +6876,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45418</v>
+        <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6897,8 +6891,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6941,7 +6940,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6955,10 +6954,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6971,7 +6970,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7014,7 +7013,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7028,10 +7027,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45763</v>
+        <v>46091</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7044,7 +7043,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7087,7 +7086,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7101,10 +7100,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>46171</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7117,7 +7116,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7160,7 +7159,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7174,10 +7173,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45796</v>
+        <v>46183</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7190,7 +7189,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7233,7 +7232,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7243,14 +7242,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45279</v>
+        <v>46185</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,7 +7262,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7306,7 +7305,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7316,14 +7315,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45813</v>
+        <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7336,7 +7335,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7396,7 +7395,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="U3" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
 Knärot
 Lakritsmusseron
 Rotfingersvamp
+Skrovlig taggsvamp
 Apelsinticka
 Blå taggsvamp
 Brunlångöra
@@ -960,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,10 +1007,10 @@
         <v>59</v>
       </c>
       <c r="T4" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="U4" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1131,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1289,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1427,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1561,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1691,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1824,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1953,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2084,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2215,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2337,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2456,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2566,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2675,7 +2676,7 @@
         <v>45779</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2786,7 +2787,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2893,7 +2894,7 @@
         <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3004,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3109,7 +3110,7 @@
         <v>44806</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3219,7 +3220,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3324,7 +3325,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3430,7 @@
         <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3535,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3748,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3826,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3904,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3977,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4050,7 +4051,7 @@
         <v>44643</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4124,7 @@
         <v>44761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4196,7 +4197,7 @@
         <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4269,7 +4270,7 @@
         <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4347,7 +4348,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4426,7 @@
         <v>45439</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4498,7 +4499,7 @@
         <v>45085</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4571,7 +4572,7 @@
         <v>45454</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4644,7 +4645,7 @@
         <v>45363</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4717,7 +4718,7 @@
         <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4790,7 +4791,7 @@
         <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4863,7 +4864,7 @@
         <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4941,7 +4942,7 @@
         <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5019,7 +5020,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5092,7 +5093,7 @@
         <v>44526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5165,7 +5166,7 @@
         <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5243,7 +5244,7 @@
         <v>45743</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5316,7 +5317,7 @@
         <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5389,7 +5390,7 @@
         <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5462,7 +5463,7 @@
         <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5535,7 +5536,7 @@
         <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5608,7 +5609,7 @@
         <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5681,7 +5682,7 @@
         <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5754,7 +5755,7 @@
         <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5832,7 +5833,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5905,7 +5906,7 @@
         <v>45302</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5978,7 +5979,7 @@
         <v>45740</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6051,7 +6052,7 @@
         <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6124,7 +6125,7 @@
         <v>45763</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6197,7 +6198,7 @@
         <v>45209</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6290,7 +6291,7 @@
         <v>45070</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6363,7 +6364,7 @@
         <v>45121</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6436,7 +6437,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6509,7 +6510,7 @@
         <v>45425</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6587,7 +6588,7 @@
         <v>44526</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6660,7 +6661,7 @@
         <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6733,7 +6734,7 @@
         <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6806,7 +6807,7 @@
         <v>45839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6879,7 +6880,7 @@
         <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6957,7 +6958,7 @@
         <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7030,7 +7031,7 @@
         <v>46091</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7103,7 +7104,7 @@
         <v>46171</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7176,7 +7177,7 @@
         <v>46183</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7249,7 +7250,7 @@
         <v>46185</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7322,7 +7323,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7395,7 +7396,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45779</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44806</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44580</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>44643</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44694</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>44825</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45439</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45085</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45454</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45363</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45324</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>44526</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45743</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45796</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45425</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45302</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45740</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45048</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45763</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45209</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45070</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45121</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45425</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44526</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46091</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>46171</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>46183</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46185</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE76"/>
+  <dimension ref="A1:AE77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="U3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,13 +1004,13 @@
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="U4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1060,6 +1060,7 @@
 Vedticka
 Västlig hakmossa
 Vågbandad barkbock
+Hultbräken
 Mattlummer
 Spillkråka
 Tjäder
@@ -1132,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1955,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2086,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2217,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2339,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2458,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2568,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2660,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21231-2025</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2673,10 +2674,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45779</v>
+        <v>45014</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2690,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2722,155 +2723,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21231-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2895,7 @@
         <v>46199</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3005,7 +3006,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3093,7 +3094,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37004-2022</t>
+          <t>A 2722-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3107,10 +3108,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44806</v>
+        <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3122,13 +3123,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3161,49 +3157,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2722-2022</t>
+          <t>A 37004-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3217,10 +3213,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44580</v>
+        <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3232,8 +3228,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3266,49 +3267,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 2722-2022 artfynd.xlsx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 37004-2022 artfynd.xlsx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 2722-2022 karta.png", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 37004-2022 karta.png", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 2722-2022 georefererad karta.tif", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 37004-2022 georefererad karta.tif", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 2722-2022 FSC-klagomål.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 37004-2022 FSC-klagomål.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 2722-2022 FSC-klagomål mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 37004-2022 FSC-klagomål mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 2722-2022 tillsynsbegäran.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 37004-2022 tillsynsbegäran.docx", "A 37004-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 2722-2022 tillsynsbegäran mail.docx", "A 2722-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 37004-2022 tillsynsbegäran mail.docx", "A 37004-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3322,10 +3323,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44796</v>
+        <v>46239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3338,19 +3339,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3362,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3378,42 +3379,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3427,10 +3428,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3443,20 +3444,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3467,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3483,35 +3484,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3535,7 +3536,7 @@
         <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3627,7 +3628,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3641,10 +3642,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46239</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3657,13 +3658,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3697,35 +3698,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3749,7 +3750,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3828,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3906,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3979,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4034,7 +4035,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 19652-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4044,14 +4045,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44643</v>
+        <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4065,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4107,7 +4108,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4121,10 +4122,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44761</v>
+        <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,8 +4137,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4180,7 +4186,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19652-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4190,14 +4196,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44694</v>
+        <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4210,7 +4216,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4253,7 +4259,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4267,10 +4273,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44825</v>
+        <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4282,13 +4288,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4348,7 +4349,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4409,7 +4410,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4423,10 +4424,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45439</v>
+        <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4438,8 +4439,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4482,7 +4488,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4502,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45085</v>
+        <v>44526</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,7 +4518,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4555,7 +4561,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4569,10 +4575,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45454</v>
+        <v>45763</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4585,7 +4591,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4628,7 +4634,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4642,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45363</v>
+        <v>46171</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4658,7 +4664,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4701,7 +4707,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4715,10 +4721,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>46183</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4731,7 +4737,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4774,7 +4780,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4788,10 +4794,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4804,7 +4810,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4847,7 +4853,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4857,14 +4863,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45425</v>
+        <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4876,13 +4882,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4925,7 +4926,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4939,10 +4940,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45324</v>
+        <v>45796</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4952,11 +4953,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5003,7 +4999,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5017,10 +5013,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>45279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5033,7 +5029,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5076,7 +5072,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5086,14 +5082,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44526</v>
+        <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5106,7 +5102,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5149,7 +5145,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5163,10 +5159,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45333</v>
+        <v>46239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5178,13 +5174,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5227,7 +5218,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5241,10 +5232,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45743</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5257,7 +5248,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5300,7 +5291,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5314,10 +5305,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45418</v>
+        <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5330,7 +5321,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5373,7 +5364,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5387,10 +5378,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45089</v>
+        <v>44643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5403,7 +5394,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5446,7 +5437,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5460,10 +5451,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45796</v>
+        <v>45209</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5476,7 +5467,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5515,11 +5506,31 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
+      <c r="Z50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5533,10 +5544,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45279</v>
+        <v>46307</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5549,7 +5560,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5592,7 +5603,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5606,10 +5617,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5622,7 +5633,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5665,7 +5676,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5675,14 +5686,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45813</v>
+        <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5695,7 +5706,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5738,7 +5749,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5752,10 +5763,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5767,13 +5778,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5816,7 +5822,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5830,10 +5836,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45775</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5846,7 +5852,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5889,7 +5895,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5903,10 +5909,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45302</v>
+        <v>45425</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5918,8 +5924,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5962,7 +5973,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5976,10 +5987,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45740</v>
+        <v>45425</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5991,8 +6002,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6035,7 +6051,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6049,10 +6065,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45048</v>
+        <v>45763</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6065,7 +6081,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6108,7 +6124,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6122,10 +6138,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45763</v>
+        <v>45425</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6137,8 +6153,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6181,7 +6202,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6195,10 +6216,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45209</v>
+        <v>45439</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6211,7 +6232,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6250,31 +6271,11 @@
         <v>0</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
-      <c r="Z60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6288,10 +6289,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45070</v>
+        <v>45333</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6303,8 +6304,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6347,7 +6353,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6361,10 +6367,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45121</v>
+        <v>45454</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6377,7 +6383,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6420,7 +6426,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6434,10 +6440,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>44526</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6450,7 +6456,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6493,7 +6499,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6507,10 +6513,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45425</v>
+        <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6522,13 +6528,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6571,7 +6572,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6585,10 +6586,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44526</v>
+        <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6601,7 +6602,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6644,7 +6645,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6658,10 +6659,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45936</v>
+        <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6674,7 +6675,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6717,7 +6718,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6731,10 +6732,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44643</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6747,7 +6748,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6790,7 +6791,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6804,10 +6805,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45839</v>
+        <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6820,7 +6821,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6863,7 +6864,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6877,10 +6878,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45351</v>
+        <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6892,13 +6893,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6941,7 +6937,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6955,10 +6951,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6971,7 +6967,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7014,7 +7010,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7028,10 +7024,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46091</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7044,7 +7040,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7087,7 +7083,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7101,10 +7097,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46171</v>
+        <v>45351</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7116,8 +7112,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7160,7 +7161,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7174,10 +7175,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46183</v>
+        <v>45048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7233,7 +7234,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7243,14 +7244,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46185</v>
+        <v>45089</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,7 +7264,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7306,7 +7307,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7320,10 +7321,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46239</v>
+        <v>45679</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7336,7 +7337,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7376,78 +7377,151 @@
       </c>
       <c r="V75" s="2" t="inlineStr"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
+          <t>A 17765-2024</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>45418</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>S 1718-2026</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D76" s="1" t="n">
+      <c r="D77" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E76" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="E77" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I77" t="n">
         <v>1.9</v>
       </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="U3" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,6 @@
 Knärot
 Lakritsmusseron
 Rotfingersvamp
-Skrovlig taggsvamp
 Apelsinticka
 Blå taggsvamp
 Brunlångöra
@@ -961,7 +960,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1007,10 +1006,10 @@
         <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="U4" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1133,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2086,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2217,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2339,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2458,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2568,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2677,7 +2676,7 @@
         <v>45014</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2767,7 +2766,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 21231-2025</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2777,14 +2776,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45779</v>
+        <v>46199</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2797,13 +2796,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -2833,156 +2832,156 @@
         <v>3</v>
       </c>
       <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 21231-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Spillkråka
 Trana</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 21231-2025 artfynd.xlsx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 21231-2025 karta.png", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 21231-2025 georefererad karta.tif", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 21231-2025 FSC-klagomål.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 21231-2025 FSC-klagomål mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 21231-2025 tillsynsbegäran.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 21231-2025 tillsynsbegäran mail.docx", "A 21231-2025")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 21231-2025 prioriterade fågelarter.docx", "A 21231-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -3006,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3111,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3216,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3308,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3323,10 +3322,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46239</v>
+        <v>45259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3339,13 +3338,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3379,42 +3378,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3428,10 +3427,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44796</v>
+        <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,19 +3443,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3471,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3484,42 +3483,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3533,10 +3536,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3549,19 +3552,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3576,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3589,46 +3592,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3642,10 +3641,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3658,13 +3657,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3698,35 +3697,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3750,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3906,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3979,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4052,7 +4051,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4125,7 +4124,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4185,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4200,10 +4199,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4216,7 +4215,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4259,7 +4258,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4273,10 +4272,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4288,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4349,7 +4348,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4409,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4424,10 +4423,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45324</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4439,13 +4438,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4488,7 +4482,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4502,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44526</v>
+        <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4518,7 +4512,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4561,7 +4555,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4575,10 +4569,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45763</v>
+        <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4591,7 +4585,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4634,7 +4628,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4642,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46171</v>
+        <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,7 +4658,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4707,7 +4701,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4721,10 +4715,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46183</v>
+        <v>44526</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4737,7 +4731,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4780,7 +4774,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4790,14 +4784,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45363</v>
+        <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4810,7 +4804,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4853,7 +4847,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4863,14 +4857,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46185</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4883,7 +4877,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4926,7 +4920,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4940,10 +4934,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45796</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4956,7 +4950,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4999,7 +4993,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5013,10 +5007,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45279</v>
+        <v>45425</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5028,8 +5022,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5072,7 +5071,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5082,14 +5081,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45813</v>
+        <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5102,7 +5101,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5145,7 +5144,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5159,10 +5158,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46239</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5175,7 +5174,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5214,11 +5213,31 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
+      <c r="Z46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5232,10 +5251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5248,7 +5267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5291,7 +5310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5305,10 +5324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46091</v>
+        <v>45121</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5321,7 +5340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5364,7 +5383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5378,10 +5397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44643</v>
+        <v>45439</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5394,7 +5413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5437,7 +5456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5451,10 +5470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45209</v>
+        <v>45936</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5467,7 +5486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5506,31 +5525,11 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
-      <c r="Z50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5544,10 +5543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46307</v>
+        <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5559,8 +5558,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5603,7 +5607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5617,10 +5621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45839</v>
+        <v>45324</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5632,8 +5636,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5676,7 +5685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5690,10 +5699,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45070</v>
+        <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5706,7 +5715,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5749,7 +5758,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5763,10 +5772,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45936</v>
+        <v>45418</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5779,7 +5788,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5848,7 @@
         <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5895,7 +5904,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5909,10 +5918,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45425</v>
+        <v>45089</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5924,13 +5933,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5973,7 +5977,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5987,10 +5991,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45425</v>
+        <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6002,13 +6006,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6051,7 +6050,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6065,10 +6064,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45763</v>
+        <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6081,7 +6080,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6124,7 +6123,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6138,10 +6137,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45425</v>
+        <v>46183</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6153,13 +6152,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6202,7 +6196,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6212,14 +6206,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45439</v>
+        <v>46185</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6232,7 +6226,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6275,7 +6269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6289,10 +6283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45333</v>
+        <v>45302</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6304,13 +6298,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6353,7 +6342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6367,10 +6356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45454</v>
+        <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6383,7 +6372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6426,7 +6415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6440,10 +6429,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44526</v>
+        <v>45763</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6456,7 +6445,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6499,7 +6488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6513,10 +6502,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45121</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6529,7 +6518,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6572,7 +6561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6586,10 +6575,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>45425</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6601,8 +6590,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6645,7 +6639,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6659,10 +6653,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45775</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6675,7 +6669,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6718,7 +6712,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,10 +6726,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6748,7 +6742,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6791,7 +6785,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6805,10 +6799,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45302</v>
+        <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6820,8 +6814,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6881,7 +6880,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6937,7 +6936,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6951,10 +6950,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45251</v>
+        <v>45454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6967,7 +6966,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7010,7 +7009,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7024,10 +7023,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>45363</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7040,7 +7039,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7083,7 +7082,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7097,10 +7096,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45351</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7112,13 +7111,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7161,7 +7155,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7175,10 +7169,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45048</v>
+        <v>45610</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7191,7 +7185,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7234,7 +7228,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7248,10 +7242,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45089</v>
+        <v>45333</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,8 +7257,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7307,7 +7306,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7321,10 +7320,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45679</v>
+        <v>45743</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7337,7 +7336,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7380,7 +7379,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7394,10 +7393,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45418</v>
+        <v>46307</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7410,7 +7409,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7470,7 +7469,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2722,155 +2722,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3338,20 +3338,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3378,35 +3378,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3592,35 +3592,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44643</v>
+        <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44806</v>
+        <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4360,13 +4360,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4409,7 +4404,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4423,10 +4418,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4439,7 +4434,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4482,7 +4477,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4491,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45763</v>
+        <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4511,8 +4506,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4555,7 +4555,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45796</v>
+        <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4584,8 +4584,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4628,7 +4633,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4638,14 +4643,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45279</v>
+        <v>45813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4658,7 +4663,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4701,7 +4706,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4715,10 +4720,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44526</v>
+        <v>45363</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4731,7 +4736,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4774,7 +4779,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4784,14 +4789,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45813</v>
+        <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4803,8 +4808,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4864,7 +4874,7 @@
         <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4920,7 +4930,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4934,10 +4944,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4950,7 +4960,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4993,7 +5003,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5007,10 +5017,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45425</v>
+        <v>44643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5022,13 +5032,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5071,7 +5076,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5085,10 +5090,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46091</v>
+        <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5100,8 +5105,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5161,7 +5171,7 @@
         <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5237,7 +5247,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45070</v>
+        <v>45439</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5267,7 +5277,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5310,7 +5320,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5324,10 +5334,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45121</v>
+        <v>45070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5340,7 +5350,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5383,7 +5393,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5397,10 +5407,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45439</v>
+        <v>46091</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5413,7 +5423,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5456,7 +5466,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5470,10 +5480,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45936</v>
+        <v>45333</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5485,8 +5495,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5529,7 +5544,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5543,10 +5558,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45425</v>
+        <v>45454</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5558,13 +5573,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5607,7 +5617,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5621,10 +5631,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45324</v>
+        <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5642,7 +5652,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5702,7 +5712,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5758,7 +5768,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5772,10 +5782,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45418</v>
+        <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5788,7 +5798,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5831,7 +5841,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5845,10 +5855,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45936</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5861,7 +5871,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5904,7 +5914,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5918,10 +5928,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45089</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5934,7 +5944,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5977,7 +5987,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5991,10 +6001,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45775</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6007,7 +6017,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6050,7 +6060,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6064,10 +6074,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46171</v>
+        <v>45743</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6080,7 +6090,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6123,7 +6133,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6137,10 +6147,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6153,7 +6163,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6196,7 +6206,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6206,14 +6216,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46185</v>
+        <v>45775</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6226,7 +6236,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6269,7 +6279,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6283,10 +6293,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45302</v>
+        <v>45281</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6299,7 +6309,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6342,7 +6352,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6356,10 +6366,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45048</v>
+        <v>45302</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6372,7 +6382,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6415,7 +6425,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6429,10 +6439,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45763</v>
+        <v>45085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6445,7 +6455,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6488,7 +6498,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6502,10 +6512,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>46183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6518,7 +6528,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6561,7 +6571,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6575,10 +6585,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45425</v>
+        <v>45251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6590,13 +6600,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6639,7 +6644,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6649,14 +6654,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44526</v>
+        <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6669,7 +6674,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6712,7 +6717,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6726,10 +6731,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44643</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6742,7 +6747,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6802,7 +6807,7 @@
         <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6863,7 +6868,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6877,10 +6882,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45085</v>
+        <v>45048</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6893,7 +6898,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6936,7 +6941,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6950,10 +6955,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45454</v>
+        <v>45089</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6966,7 +6971,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7009,7 +7014,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7023,10 +7028,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45363</v>
+        <v>45679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7039,7 +7044,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7082,7 +7087,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7096,10 +7101,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>45418</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7112,7 +7117,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7155,7 +7160,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7169,10 +7174,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45610</v>
+        <v>46239</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7228,7 +7233,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7242,10 +7247,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45333</v>
+        <v>44526</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7257,13 +7262,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7306,7 +7306,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45743</v>
+        <v>45763</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>46307</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AE79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T3" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="U3" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
 Knärot
 Lakritsmusseron
 Rotfingersvamp
+Skrovlig taggsvamp
 Apelsinticka
 Blå taggsvamp
 Brunlångöra
@@ -960,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1006,10 +1007,10 @@
         <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="U4" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1290,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1428,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1562,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1692,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1825,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1954,7 +1955,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2085,7 +2086,7 @@
         <v>45991</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2216,7 +2217,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2338,7 +2339,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2457,7 +2458,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2567,7 +2568,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2660,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2669,14 +2670,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2689,13 +2690,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2722,155 +2723,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2895,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3005,7 +3006,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3110,7 +3111,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3215,7 +3216,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3326,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3414,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3427,10 +3428,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3443,7 +3444,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3452,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3467,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3483,46 +3484,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3536,10 +3533,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,7 +3549,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3561,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3576,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3592,35 +3589,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3645,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3749,7 +3750,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3827,7 +3828,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3905,7 +3906,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3979,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4052,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4124,7 +4125,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4203,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4276,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4331,7 +4332,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4345,10 +4346,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45796</v>
+        <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4360,8 +4361,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4421,7 +4427,7 @@
         <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4477,7 +4483,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4491,10 +4497,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45324</v>
+        <v>45209</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,13 +4512,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4551,11 +4552,31 @@
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
+      <c r="Z37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4569,10 +4590,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44806</v>
+        <v>45070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4584,13 +4605,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4633,7 +4649,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4643,14 +4659,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45813</v>
+        <v>45121</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,7 +4679,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4706,7 +4722,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4720,10 +4736,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45363</v>
+        <v>45679</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4736,7 +4752,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4779,7 +4795,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4789,14 +4805,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45425</v>
+        <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4808,13 +4824,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4857,7 +4868,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4871,10 +4882,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>45439</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4887,7 +4898,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4930,7 +4941,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4947,7 +4958,7 @@
         <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4960,7 +4971,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5003,7 +5014,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5017,10 +5028,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44643</v>
+        <v>45740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5033,7 +5044,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5076,7 +5087,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5093,7 +5104,7 @@
         <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5111,7 +5122,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5154,7 +5165,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5168,10 +5179,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>44526</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5184,7 +5195,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5223,31 +5234,11 @@
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr"/>
-      <c r="Z46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5261,10 +5252,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45439</v>
+        <v>45324</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5276,8 +5267,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5320,7 +5316,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5334,10 +5330,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45070</v>
+        <v>45418</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5350,7 +5346,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5393,7 +5389,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5407,10 +5403,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46091</v>
+        <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5423,7 +5419,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5466,7 +5462,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5480,10 +5476,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45333</v>
+        <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5495,13 +5491,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5544,7 +5535,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5558,10 +5549,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45454</v>
+        <v>45425</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5573,8 +5564,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5617,7 +5613,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5631,10 +5627,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5646,13 +5642,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5695,7 +5686,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5709,10 +5700,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45839</v>
+        <v>45775</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5725,7 +5716,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5768,7 +5759,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5782,10 +5773,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44526</v>
+        <v>45839</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5798,7 +5789,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5841,7 +5832,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5855,10 +5846,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45936</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5871,7 +5862,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5914,7 +5905,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5928,10 +5919,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45302</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5944,7 +5935,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5987,7 +5978,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6001,10 +5992,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45121</v>
+        <v>45048</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6060,7 +6051,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6074,10 +6065,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45743</v>
+        <v>45763</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6090,7 +6081,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6133,7 +6124,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6147,10 +6138,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6163,7 +6154,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6206,7 +6197,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6220,10 +6211,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45775</v>
+        <v>46171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6236,7 +6227,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6279,7 +6270,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6293,10 +6284,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45281</v>
+        <v>45425</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6308,8 +6299,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6352,7 +6348,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6366,10 +6362,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45302</v>
+        <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6382,7 +6378,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6425,7 +6421,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6439,10 +6435,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45085</v>
+        <v>44526</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6455,7 +6451,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6498,7 +6494,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6508,14 +6504,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6528,7 +6524,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6571,7 +6567,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6585,10 +6581,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45251</v>
+        <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6601,7 +6597,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6644,7 +6640,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6654,14 +6650,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46185</v>
+        <v>45351</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6673,8 +6669,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6717,7 +6718,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6731,10 +6732,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>45085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6747,7 +6748,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6790,7 +6791,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6804,10 +6805,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45351</v>
+        <v>45454</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6819,13 +6820,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6868,7 +6864,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6882,10 +6878,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45048</v>
+        <v>45363</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6898,7 +6894,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6941,7 +6937,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6955,10 +6951,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45089</v>
+        <v>46239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6971,7 +6967,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7014,7 +7010,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7028,10 +7024,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45679</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7044,7 +7040,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7087,7 +7083,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7101,10 +7097,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45418</v>
+        <v>45333</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7116,8 +7112,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7160,7 +7161,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7174,10 +7175,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46239</v>
+        <v>45743</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7190,7 +7191,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7233,7 +7234,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7247,10 +7248,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44526</v>
+        <v>45796</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,7 +7264,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7306,7 +7307,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7320,10 +7321,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45763</v>
+        <v>46307</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7336,7 +7337,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7379,7 +7380,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 42952-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7393,134 +7394,280 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="E76" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A 42975-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
         <v>46310</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="E77" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A 12787-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>S 1718-2026</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D77" s="1" t="n">
+      <c r="D79" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E77" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
+      <c r="E79" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
         <v>1.9</v>
       </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17454-2026</t>
+          <t>A 59567-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46120</v>
+        <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>31.4</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -2001,12 +2001,143 @@
         <v>19</v>
       </c>
       <c r="T11" t="n">
+        <v>33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>28</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Fjällig taggsvamp s.str.
+Kandelabersvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vintertagging
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Brandticka
+Grovticka
+Grön sköldmossa
+Jättesvampmal
+Mindre märgborre
+Vågbandad barkbock
+Spillkråka
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 17454-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19</v>
+      </c>
+      <c r="T12" t="n">
         <v>32</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>24</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -2029,171 +2160,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 17454-2026 artfynd.xlsx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 17454-2026 karta.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 17454-2026 georefererad karta.tif", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 17454-2026 karta knärot.png", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 17454-2026 FSC-klagomål.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 17454-2026 FSC-klagomål mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 17454-2026 tillsynsbegäran.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 17454-2026 tillsynsbegäran mail.docx", "A 17454-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 17454-2026 prioriterade fågelarter.docx", "A 17454-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 59567-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>19</v>
-      </c>
-      <c r="T12" t="n">
-        <v>33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>28</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Fjällig taggsvamp s.str.
-Kandelabersvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vintertagging
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Brandticka
-Grovticka
-Grön sköldmossa
-Jättesvampmal
-Mindre märgborre
-Vågbandad barkbock
-Spillkråka
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 59567-2025 artfynd.xlsx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 59567-2025 karta.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 59567-2025 georefererad karta.tif", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 59567-2025 karta knärot.png", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 59567-2025 FSC-klagomål.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 59567-2025 FSC-klagomål mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 59567-2025 tillsynsbegäran.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 59567-2025 tillsynsbegäran mail.docx", "A 59567-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 59567-2025 prioriterade fågelarter.docx", "A 59567-2025")</f>
         <v/>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14729-2023</t>
+          <t>A 28861-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2723,155 +2723,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogshare
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 14729-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45014</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3484,42 +3484,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3533,10 +3537,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44966</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3549,7 +3553,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3558,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3573,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3589,39 +3593,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45279</v>
+        <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4439,8 +4439,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4483,7 +4488,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4497,10 +4502,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45209</v>
+        <v>45363</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4513,7 +4518,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4552,31 +4557,11 @@
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
-      <c r="Z37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4590,10 +4575,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45070</v>
+        <v>44643</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4591,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4649,7 +4634,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4663,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45121</v>
+        <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4679,7 +4664,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4718,11 +4703,31 @@
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45679</v>
+        <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4752,7 +4757,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4795,7 +4800,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4805,14 +4810,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45813</v>
+        <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4824,8 +4829,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4868,7 +4878,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4882,10 +4892,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4898,7 +4908,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4941,7 +4951,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4955,10 +4965,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45763</v>
+        <v>45936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4971,7 +4981,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5014,7 +5024,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5028,10 +5038,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45740</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5044,7 +5054,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5087,7 +5097,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5104,7 +5114,7 @@
         <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5122,7 +5132,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5165,7 +5175,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5179,10 +5189,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44526</v>
+        <v>45763</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5195,7 +5205,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5238,7 +5248,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5252,10 +5262,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45324</v>
+        <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5273,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5316,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5330,10 +5340,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45418</v>
+        <v>45439</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5346,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5389,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5403,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45089</v>
+        <v>45333</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5418,8 +5428,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5462,7 +5477,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5476,10 +5491,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45251</v>
+        <v>45454</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5492,7 +5507,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5535,7 +5550,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5549,10 +5564,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45425</v>
+        <v>44526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5564,13 +5579,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5613,7 +5623,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5627,10 +5637,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45936</v>
+        <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5643,7 +5653,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5686,7 +5696,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5700,10 +5710,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45775</v>
+        <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5716,7 +5726,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5759,7 +5769,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5773,10 +5783,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45839</v>
+        <v>45743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5789,7 +5799,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5832,7 +5842,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5846,10 +5856,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5862,7 +5872,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5905,7 +5915,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5919,10 +5929,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45302</v>
+        <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5935,7 +5945,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5978,7 +5988,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5992,10 +6002,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45048</v>
+        <v>45281</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6008,7 +6018,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6051,7 +6061,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6061,14 +6071,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45763</v>
+        <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6081,7 +6091,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6124,7 +6134,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6138,10 +6148,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45281</v>
+        <v>45302</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6154,7 +6164,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6197,7 +6207,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6211,10 +6221,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46171</v>
+        <v>45085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6227,7 +6237,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6270,7 +6280,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6284,10 +6294,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45425</v>
+        <v>45251</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6299,13 +6309,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6348,7 +6353,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6362,10 +6367,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46183</v>
+        <v>46091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6378,7 +6383,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6421,7 +6426,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6435,10 +6440,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44526</v>
+        <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6451,7 +6456,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6494,7 +6499,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6504,14 +6509,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46185</v>
+        <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6523,8 +6528,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6567,7 +6577,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6581,10 +6591,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44643</v>
+        <v>45048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6597,7 +6607,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6640,7 +6650,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6654,10 +6664,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45351</v>
+        <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6669,13 +6679,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6718,7 +6723,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,10 +6737,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45085</v>
+        <v>45679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6748,7 +6753,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6791,7 +6796,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6805,10 +6810,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45454</v>
+        <v>45418</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6821,7 +6826,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6864,7 +6869,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6878,10 +6883,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45363</v>
+        <v>46239</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6894,7 +6899,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6937,7 +6942,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6951,10 +6956,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46239</v>
+        <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6967,7 +6972,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7010,7 +7015,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7024,10 +7029,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>45763</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7040,7 +7045,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7083,7 +7088,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7097,10 +7102,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45333</v>
+        <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7112,13 +7117,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45743</v>
+        <v>46307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45796</v>
+        <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7307,7 +7307,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7317,14 +7317,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46307</v>
+        <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>46310</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46091</v>
+        <v>45740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7616,7 +7616,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1992,25 +1992,26 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Fjällig taggsvamp s.str.
 Kandelabersvamp
+Rödfläckig zontaggsvamp
 Tallticka
 Talltita
 Tjockfotad fingersvamp
@@ -2086,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2217,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2263,10 +2264,10 @@
         <v>14</v>
       </c>
       <c r="T13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -2339,7 +2340,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2458,7 +2459,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2568,7 +2569,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2677,7 +2678,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2788,7 +2789,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2895,7 +2896,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3006,7 +3007,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3111,7 +3112,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3216,7 +3217,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3326,7 +3327,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3431,7 +3432,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3540,7 +3541,7 @@
         <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3645,7 +3646,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3750,7 +3751,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3829,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3906,7 +3907,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3979,7 +3980,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4052,7 +4053,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4125,7 +4126,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4204,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4276,7 +4277,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4349,7 +4350,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4427,7 +4428,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4505,7 +4506,7 @@
         <v>45363</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4578,7 +4579,7 @@
         <v>44643</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4651,7 +4652,7 @@
         <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4744,7 +4745,7 @@
         <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4817,7 +4818,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4895,7 +4896,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4968,7 +4969,7 @@
         <v>45936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5041,7 +5042,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5114,7 +5115,7 @@
         <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5192,7 +5193,7 @@
         <v>45763</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5265,7 +5266,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5343,7 +5344,7 @@
         <v>45439</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5416,7 +5417,7 @@
         <v>45333</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5494,7 +5495,7 @@
         <v>45454</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5567,7 +5568,7 @@
         <v>44526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5640,7 +5641,7 @@
         <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5713,7 +5714,7 @@
         <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5786,7 +5787,7 @@
         <v>45743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5859,7 +5860,7 @@
         <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5932,7 +5933,7 @@
         <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6005,7 +6006,7 @@
         <v>45281</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6078,7 +6079,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6151,7 +6152,7 @@
         <v>45302</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6224,7 +6225,7 @@
         <v>45085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6297,7 +6298,7 @@
         <v>45251</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6370,7 +6371,7 @@
         <v>46091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6443,7 +6444,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6516,7 +6517,7 @@
         <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6595,7 @@
         <v>45048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6667,7 +6668,7 @@
         <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6741,7 @@
         <v>45679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6814,7 @@
         <v>45418</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6887,7 @@
         <v>46239</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6960,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7032,7 +7033,7 @@
         <v>45763</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7106,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7179,7 @@
         <v>46307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7251,7 +7252,7 @@
         <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7324,7 +7325,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7398,7 @@
         <v>46310</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7471,7 @@
         <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7543,7 +7544,7 @@
         <v>45740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7616,7 +7617,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45363</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44643</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45763</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45439</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45333</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45454</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44526</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45281</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45302</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45251</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>46091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>45089</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45418</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>46239</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>45763</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>46307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>46310</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>45740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28861-2026</t>
+          <t>A 14729-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2691,13 +2691,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2724,155 +2724,155 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Granbarkgnagare
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Skogshare
 Grovticka
 Nattskärra</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 14729-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45014</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Granbarkgnagare
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3380,35 +3380,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3554,20 +3554,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3594,35 +3594,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45324</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4440,13 +4440,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4489,7 +4484,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4519,7 +4514,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44643</v>
+        <v>44526</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45209</v>
+        <v>45251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4665,7 +4660,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4704,31 +4699,11 @@
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
-      <c r="Z39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4742,10 +4717,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45070</v>
+        <v>45425</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4757,8 +4732,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4801,7 +4781,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4815,10 +4795,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45425</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4830,13 +4810,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4879,7 +4854,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4893,10 +4868,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45209</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4909,7 +4884,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4948,11 +4923,31 @@
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
+      <c r="Z42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4966,10 +4961,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45936</v>
+        <v>45070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4977,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5025,7 +5020,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5039,10 +5034,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5050,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5098,7 +5093,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5112,10 +5107,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45425</v>
+        <v>45610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5127,13 +5122,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5176,7 +5166,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5190,10 +5180,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45763</v>
+        <v>45439</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5206,7 +5196,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5249,7 +5239,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5266,7 +5256,7 @@
         <v>45425</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5284,7 +5274,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5327,7 +5317,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5341,10 +5331,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45439</v>
+        <v>45324</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,8 +5346,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5400,7 +5395,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5414,10 +5409,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45333</v>
+        <v>45418</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5429,13 +5424,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5478,7 +5468,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5492,10 +5482,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45454</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5508,7 +5498,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5551,7 +5541,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5565,10 +5555,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44526</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5581,7 +5571,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5624,7 +5614,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5638,10 +5628,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46171</v>
+        <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5654,7 +5644,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5697,7 +5687,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5711,10 +5701,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45121</v>
+        <v>46183</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5770,7 +5760,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5780,14 +5770,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45743</v>
+        <v>46185</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5800,7 +5790,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5843,7 +5833,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5857,10 +5847,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46183</v>
+        <v>46091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5873,7 +5863,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5916,7 +5906,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5930,10 +5920,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45775</v>
+        <v>45302</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5946,7 +5936,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5989,7 +5979,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6003,10 +5993,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45281</v>
+        <v>45048</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6019,7 +6009,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6062,7 +6052,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6072,14 +6062,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46185</v>
+        <v>45763</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6092,7 +6082,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6135,7 +6125,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6149,10 +6139,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45302</v>
+        <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6165,7 +6155,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6208,7 +6198,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6222,10 +6212,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45085</v>
+        <v>45425</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6237,8 +6227,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45251</v>
+        <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46091</v>
+        <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6384,7 +6379,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6427,7 +6422,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45610</v>
+        <v>44643</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6457,7 +6452,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6517,7 +6512,7 @@
         <v>45351</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6578,7 +6573,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6592,10 +6587,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45048</v>
+        <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6608,7 +6603,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6651,7 +6646,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6665,10 +6660,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45089</v>
+        <v>45454</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6681,7 +6676,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6724,7 +6719,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6738,10 +6733,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45679</v>
+        <v>45363</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6754,7 +6749,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6797,7 +6792,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6811,10 +6806,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45418</v>
+        <v>46239</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6827,7 +6822,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6870,7 +6865,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6884,10 +6879,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46239</v>
+        <v>45610</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6943,7 +6938,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6957,10 +6952,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44526</v>
+        <v>45333</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6972,8 +6967,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45763</v>
+        <v>45743</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46307</v>
+        <v>45279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45279</v>
+        <v>46307</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7325,7 +7325,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>46310</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>45740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2661,218 +2661,220 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
+          <t>A 28861-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Skogshare
+Tallticka
+Grovticka
+Nattskärra</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>A 14729-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45014</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 14729-2023 artfynd.xlsx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 14729-2023 karta.png", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 14729-2023 georefererad karta.tif", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 14729-2023 FSC-klagomål.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 14729-2023 FSC-klagomål mail.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 14729-2023 tillsynsbegäran.docx", "A 14729-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 14729-2023 tillsynsbegäran mail.docx", "A 14729-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 28861-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HANINGE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogshare
-Grovticka
-Nattskärra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 28861-2026 artfynd.xlsx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 28861-2026 karta.png", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 28861-2026 georefererad karta.tif", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 28861-2026 FSC-klagomål.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 28861-2026 FSC-klagomål mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 28861-2026 tillsynsbegäran.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 28861-2026 tillsynsbegäran mail.docx", "A 28861-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 28861-2026 prioriterade fågelarter.docx", "A 28861-2026")</f>
         <v/>
       </c>
     </row>
@@ -2896,7 +2898,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3007,7 +3009,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3112,7 +3114,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3219,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3310,7 +3312,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3324,10 +3326,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3340,20 +3342,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3364,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3380,35 +3382,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3432,7 +3434,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3524,7 +3526,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3538,10 +3540,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3554,10 +3556,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3566,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3578,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3594,35 +3596,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3646,7 +3648,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3751,7 +3753,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3829,7 +3831,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3907,7 +3909,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3980,7 +3982,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4055,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4128,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4206,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4277,7 +4279,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4350,7 +4352,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4411,7 +4413,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4425,10 +4427,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4440,8 +4442,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4484,7 +4491,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4498,10 +4505,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4514,7 +4521,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4557,7 +4564,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4571,10 +4578,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44526</v>
+        <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4587,7 +4594,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4630,7 +4637,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4644,10 +4651,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45251</v>
+        <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4660,7 +4667,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4703,7 +4710,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4717,10 +4724,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45425</v>
+        <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4732,13 +4739,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4781,7 +4783,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4791,14 +4793,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4811,7 +4813,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4871,7 +4873,7 @@
         <v>45209</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4964,7 +4966,7 @@
         <v>45070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5020,7 +5022,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5034,10 +5036,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45121</v>
+        <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5050,7 +5052,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5093,7 +5095,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5107,10 +5109,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45610</v>
+        <v>45425</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5122,8 +5124,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5166,7 +5173,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5180,10 +5187,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5196,7 +5203,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5239,7 +5246,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5253,10 +5260,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45425</v>
+        <v>45740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5268,13 +5275,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5317,7 +5319,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5331,10 +5333,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45324</v>
+        <v>45936</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5346,13 +5348,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5395,7 +5392,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5409,10 +5406,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45418</v>
+        <v>45610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5422,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5468,7 +5465,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5482,10 +5479,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46171</v>
+        <v>45425</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5497,8 +5494,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5541,7 +5543,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5555,10 +5557,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5571,7 +5573,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5614,7 +5616,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5628,10 +5630,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45775</v>
+        <v>45425</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5643,8 +5645,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5687,7 +5694,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5701,10 +5708,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46183</v>
+        <v>45439</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5717,7 +5724,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5760,7 +5767,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5770,14 +5777,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46185</v>
+        <v>45333</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5789,8 +5796,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5833,7 +5845,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5847,10 +5859,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46091</v>
+        <v>46171</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5863,7 +5875,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5906,7 +5918,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5920,10 +5932,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45302</v>
+        <v>45454</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5936,7 +5948,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5979,7 +5991,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5993,10 +6005,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45048</v>
+        <v>44526</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6009,7 +6021,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6052,7 +6064,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6066,10 +6078,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45763</v>
+        <v>46183</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6082,7 +6094,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6125,7 +6137,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6135,14 +6147,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45281</v>
+        <v>46185</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6155,7 +6167,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6198,7 +6210,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6212,10 +6224,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45425</v>
+        <v>45121</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6227,13 +6239,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6276,7 +6283,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6290,10 +6297,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45936</v>
+        <v>45743</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6306,7 +6313,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6349,7 +6356,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6363,10 +6370,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44526</v>
+        <v>45775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6379,7 +6386,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6422,7 +6429,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6436,10 +6443,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44643</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6452,7 +6459,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6495,7 +6502,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6509,10 +6516,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45351</v>
+        <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6524,13 +6531,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6590,7 +6592,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6646,7 +6648,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6660,10 +6662,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45454</v>
+        <v>45251</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6676,7 +6678,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6719,7 +6721,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6733,10 +6735,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45363</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6749,7 +6751,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6809,7 +6811,7 @@
         <v>46239</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6865,7 +6867,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6879,10 +6881,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45610</v>
+        <v>45351</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6894,8 +6896,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6938,7 +6945,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6952,10 +6959,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45333</v>
+        <v>45048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6967,13 +6974,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7016,7 +7018,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7030,10 +7032,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45743</v>
+        <v>45089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7046,7 +7048,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7089,7 +7091,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7103,10 +7105,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45796</v>
+        <v>45679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7119,7 +7121,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7162,7 +7164,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7176,10 +7178,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45279</v>
+        <v>45418</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7192,7 +7194,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7252,7 +7254,7 @@
         <v>46307</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7308,7 +7310,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 42952-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7318,14 +7320,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45813</v>
+        <v>46310</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7338,7 +7340,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7381,7 +7383,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42952-2026</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7395,10 +7397,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46310</v>
+        <v>44526</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7411,7 +7413,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7454,7 +7456,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42975-2026</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7468,10 +7470,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46310</v>
+        <v>45763</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7484,7 +7486,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7527,7 +7529,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 42975-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7541,10 +7543,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45740</v>
+        <v>46310</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7557,7 +7559,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7617,7 +7619,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2255,26 +2255,28 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T13" t="n">
+        <v>27</v>
+      </c>
+      <c r="U13" t="n">
         <v>25</v>
       </c>
-      <c r="U13" t="n">
-        <v>23</v>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp
+Dropptaggsvamp
 Tallkötticka
 Talltita
 Ullticka
+Blåmossa
 Grön sköldmossa
 Grönpyrola
 Kornknutmossa
@@ -2340,7 +2342,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2459,7 +2461,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2569,7 +2571,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2678,7 +2680,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2791,7 +2793,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2898,7 +2900,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3009,7 +3011,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3114,7 +3116,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3219,7 +3221,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3312,7 +3314,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34823-2022</t>
+          <t>A 60369-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3326,10 +3328,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44796</v>
+        <v>45259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3342,10 +3344,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3354,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3366,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3382,35 +3384,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3436,7 @@
         <v>44966</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3526,7 +3528,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60369-2023</t>
+          <t>A 34823-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3540,10 +3542,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,20 +3558,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3580,10 +3582,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3596,35 +3598,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 60369-2023 artfynd.xlsx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 34823-2022 artfynd.xlsx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 60369-2023 karta.png", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 34823-2022 karta.png", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 60369-2023 georefererad karta.tif", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 34823-2022 georefererad karta.tif", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 60369-2023 FSC-klagomål.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 34823-2022 FSC-klagomål.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 60369-2023 FSC-klagomål mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 34823-2022 FSC-klagomål mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 60369-2023 tillsynsbegäran.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 34823-2022 tillsynsbegäran.docx", "A 34823-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 60369-2023 tillsynsbegäran mail.docx", "A 60369-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 34823-2022 tillsynsbegäran mail.docx", "A 34823-2022")</f>
         <v/>
       </c>
     </row>
@@ -3648,7 +3650,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3753,7 +3755,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3831,7 +3833,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3909,7 +3911,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3982,7 +3984,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4057,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4130,7 @@
         <v>44825</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4206,7 +4208,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4279,7 +4281,7 @@
         <v>44761</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4352,7 +4354,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4413,7 +4415,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4427,10 +4429,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45324</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,13 +4444,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4491,7 +4488,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4505,10 +4502,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4518,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4581,7 +4578,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4654,7 +4651,7 @@
         <v>45279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4707,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4724,10 +4721,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44643</v>
+        <v>44526</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4740,7 +4737,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4800,7 +4797,7 @@
         <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4856,7 +4853,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4870,10 +4867,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45209</v>
+        <v>45740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4886,7 +4883,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4925,31 +4922,11 @@
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
-      <c r="Z42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4963,10 +4940,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45070</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4979,7 +4956,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5022,7 +4999,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5036,10 +5013,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46091</v>
+        <v>45425</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,8 +5028,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5095,7 +5077,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5109,10 +5091,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45425</v>
+        <v>45209</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,13 +5106,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5169,11 +5146,31 @@
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
+      <c r="Z45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5187,10 +5184,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45839</v>
+        <v>45070</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5203,7 +5200,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5246,7 +5243,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5260,10 +5257,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45740</v>
+        <v>46091</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5276,7 +5273,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5319,7 +5316,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5333,10 +5330,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45936</v>
+        <v>45121</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5349,7 +5346,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5392,7 +5389,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52770-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5406,10 +5403,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45610</v>
+        <v>45439</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5422,7 +5419,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5465,7 +5462,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5482,7 +5479,7 @@
         <v>45425</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5500,7 +5497,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5543,7 +5540,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5557,10 +5554,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>45324</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5572,8 +5569,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5616,7 +5618,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5630,10 +5632,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45425</v>
+        <v>45936</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5645,13 +5647,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5694,7 +5691,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5708,10 +5705,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45439</v>
+        <v>45418</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5724,7 +5721,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5767,7 +5764,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5781,10 +5778,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45333</v>
+        <v>45839</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,13 +5793,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5845,7 +5837,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5859,10 +5851,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46171</v>
+        <v>45089</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5875,7 +5867,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5918,7 +5910,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 52770-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5932,10 +5924,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45454</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5948,7 +5940,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5991,7 +5983,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6005,10 +5997,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44526</v>
+        <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6021,7 +6013,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6064,7 +6056,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6078,10 +6070,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6094,7 +6086,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6137,7 +6129,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6147,14 +6139,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46185</v>
+        <v>45302</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6167,7 +6159,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6210,7 +6202,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6224,10 +6216,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45121</v>
+        <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6283,7 +6275,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6293,14 +6285,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45743</v>
+        <v>46185</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6313,7 +6305,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6356,7 +6348,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6370,10 +6362,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45775</v>
+        <v>45048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6386,7 +6378,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6429,7 +6421,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6443,10 +6435,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>45763</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6459,7 +6451,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6502,7 +6494,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6516,10 +6508,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45302</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6532,7 +6524,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6575,7 +6567,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6589,10 +6581,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45085</v>
+        <v>45425</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,8 +6596,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6648,7 +6645,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6662,10 +6659,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45251</v>
+        <v>44526</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6678,7 +6675,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6721,7 +6718,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6735,10 +6732,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>44643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6751,7 +6748,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6794,7 +6791,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6808,10 +6805,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46239</v>
+        <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6823,8 +6820,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6867,7 +6869,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6881,10 +6883,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45351</v>
+        <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,13 +6898,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6945,7 +6942,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6959,10 +6956,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45048</v>
+        <v>45454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6975,7 +6972,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7018,7 +7015,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7032,10 +7029,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45089</v>
+        <v>45363</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7048,7 +7045,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7091,7 +7088,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7105,10 +7102,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45679</v>
+        <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7121,7 +7118,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7164,7 +7161,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7178,10 +7175,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45418</v>
+        <v>45610</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7194,7 +7191,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7237,7 +7234,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7251,10 +7248,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46307</v>
+        <v>45333</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,8 +7263,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7310,7 +7312,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42952-2026</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7324,10 +7326,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46310</v>
+        <v>45743</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7340,7 +7342,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7383,7 +7385,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7397,10 +7399,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44526</v>
+        <v>46307</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7413,7 +7415,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7456,7 +7458,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 42952-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7470,10 +7472,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45763</v>
+        <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7486,7 +7488,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7546,7 +7548,7 @@
         <v>46310</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7619,7 +7621,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2234,13 +2234,13 @@
         <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -2255,24 +2255,25 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="U13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp
 Dropptaggsvamp
+Motaggsvamp
 Tallkötticka
 Talltita
 Ullticka
@@ -2285,6 +2286,7 @@
 Ekbräken
 Hultbräken
 Spillkråka
+Tofsmes
 Kopparödla
 Revlummer</t>
         </is>
@@ -2342,7 +2344,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2461,7 +2463,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2571,7 +2573,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2680,7 +2682,7 @@
         <v>46199</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2793,7 +2795,7 @@
         <v>45014</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2900,7 +2902,7 @@
         <v>45779</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3011,7 +3013,7 @@
         <v>44818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3116,7 +3118,7 @@
         <v>44580</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3221,7 +3223,7 @@
         <v>44806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3331,7 +3333,7 @@
         <v>45259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6648-2023</t>
+          <t>A 32479-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3433,10 +3435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44966</v>
+        <v>46239</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3449,16 +3451,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3473,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3489,39 +3491,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3545,7 +3543,7 @@
         <v>44796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3633,7 +3631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32479-2026</t>
+          <t>A 6648-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3647,10 +3645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46239</v>
+        <v>44966</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3663,17 +3661,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3687,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3703,35 +3701,39 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 32479-2026 artfynd.xlsx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/artfynd/A 6648-2023 artfynd.xlsx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 32479-2026 karta.png", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor/A 6648-2023 karta.png", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 32479-2026 georefererad karta.tif", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/kartor_geotiff/A 6648-2023 georefererad karta.tif", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 32479-2026 FSC-klagomål.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 6648-2023 FSC-klagomål.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 32479-2026 FSC-klagomål mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 6648-2023 FSC-klagomål mail.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 32479-2026 tillsynsbegäran.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 6648-2023 tillsynsbegäran.docx", "A 6648-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 32479-2026 tillsynsbegäran mail.docx", "A 32479-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 6648-2023 tillsynsbegäran mail.docx", "A 6648-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/fåglar/A 6648-2023 prioriterade fågelarter.docx", "A 6648-2023")</f>
         <v/>
       </c>
     </row>
@@ -3755,7 +3757,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3833,7 +3835,7 @@
         <v>44825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3911,7 +3913,7 @@
         <v>44845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3984,7 +3986,7 @@
         <v>44845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4057,7 +4059,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4113,7 +4115,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41266-2022</t>
+          <t>A 37000-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4127,10 +4129,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44825</v>
+        <v>44806</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4150,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4191,7 +4193,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13135-2022</t>
+          <t>A 41266-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4205,10 +4207,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44643</v>
+        <v>44825</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,8 +4222,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4264,7 +4271,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30419-2022</t>
+          <t>A 13135-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4278,10 +4285,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44761</v>
+        <v>44643</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4294,7 +4301,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4337,7 +4344,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37000-2022</t>
+          <t>A 30419-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4351,10 +4358,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44806</v>
+        <v>44761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4366,13 +4373,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4415,7 +4417,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3156-2025</t>
+          <t>A 33792-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4429,10 +4431,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>45121</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4447,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4488,7 +4490,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18491-2025</t>
+          <t>A 14900-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4502,10 +4504,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45763</v>
+        <v>45743</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4518,7 +4520,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4561,7 +4563,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24193-2025</t>
+          <t>A 4297-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4575,10 +4577,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45796</v>
+        <v>45324</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4588,6 +4590,11 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>HANINGE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -4634,7 +4641,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64075-2023</t>
+          <t>A 20527-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4655,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45279</v>
+        <v>45775</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,7 +4671,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4707,7 +4714,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68896-2021</t>
+          <t>A 64568-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4721,10 +4728,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44526</v>
+        <v>45281</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4737,7 +4744,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4780,7 +4787,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27596-2025</t>
+          <t>A 9946-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4790,14 +4797,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45813</v>
+        <v>45363</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4810,7 +4817,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4853,7 +4860,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14264-2025</t>
+          <t>A 27596-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4863,14 +4870,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45740</v>
+        <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4883,7 +4890,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4926,7 +4933,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58599-2023</t>
+          <t>A 1180-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4940,10 +4947,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>45302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4956,7 +4963,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4999,7 +5006,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18528-2024</t>
+          <t>A 24873-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5013,10 +5020,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45425</v>
+        <v>45085</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5028,13 +5035,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5077,7 +5079,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50306-2023</t>
+          <t>A 58599-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5091,10 +5093,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45209</v>
+        <v>45251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5107,7 +5109,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5146,31 +5148,11 @@
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
-      <c r="Z45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22288-2023</t>
+          <t>A 52836-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5184,10 +5166,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45070</v>
+        <v>45610</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5200,7 +5182,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5243,7 +5225,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12787-2026</t>
+          <t>A 8078-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5257,10 +5239,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46091</v>
+        <v>45351</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5272,8 +5254,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5316,7 +5303,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33792-2023</t>
+          <t>A 14264-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5330,10 +5317,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45121</v>
+        <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5346,7 +5333,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5389,7 +5376,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20839-2024</t>
+          <t>A 32948-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5403,10 +5390,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45439</v>
+        <v>45839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5419,7 +5406,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5462,7 +5449,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18512-2024</t>
+          <t>A 19220-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5476,10 +5463,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45425</v>
+        <v>45048</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5491,13 +5478,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5540,7 +5522,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4297-2024</t>
+          <t>A 25584-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5554,10 +5536,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45324</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5569,13 +5551,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5618,7 +5595,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48606-2025</t>
+          <t>A 3156-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5632,10 +5609,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45936</v>
+        <v>45679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5648,7 +5625,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5691,7 +5668,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17765-2024</t>
+          <t>A 48606-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5705,10 +5682,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45418</v>
+        <v>45936</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5721,7 +5698,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5764,7 +5741,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32948-2025</t>
+          <t>A 17765-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5778,10 +5755,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45839</v>
+        <v>45418</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5794,7 +5771,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5837,7 +5814,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25584-2023</t>
+          <t>A 13046-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5851,10 +5828,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45089</v>
+        <v>44643</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5867,7 +5844,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5927,7 +5904,7 @@
         <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5983,7 +5960,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20527-2025</t>
+          <t>A 68894-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5997,10 +5974,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45775</v>
+        <v>44526</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6013,7 +5990,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6056,7 +6033,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24800-2026</t>
+          <t>A 18491-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6070,10 +6047,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46171</v>
+        <v>45763</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6086,7 +6063,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6129,7 +6106,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1180-2024</t>
+          <t>A 24800-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6143,10 +6120,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45302</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6159,7 +6136,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6202,7 +6179,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26417-2026</t>
+          <t>A 50306-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6216,10 +6193,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46183</v>
+        <v>45209</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6232,7 +6209,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6271,11 +6248,31 @@
         <v>0</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
+      <c r="Z60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/knärot/A 50306-2023 karta knärot.png", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomål/A 50306-2023 FSC-klagomål.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/klagomålsmail/A 50306-2023 FSC-klagomål mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsyn/A 50306-2023 tillsynsbegäran.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0136/tillsynsmail/A 50306-2023 tillsynsbegäran mail.docx", "A 50306-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26886-2026</t>
+          <t>A 26417-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6285,14 +6282,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6305,7 +6302,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6348,7 +6345,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19220-2023</t>
+          <t>A 22288-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6362,10 +6359,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45048</v>
+        <v>45070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6378,7 +6375,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6421,7 +6418,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18490-2025</t>
+          <t>A 26886-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6431,14 +6428,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45763</v>
+        <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6451,7 +6448,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6494,7 +6491,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64568-2023</t>
+          <t>A 24193-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6508,10 +6505,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>45796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6524,7 +6521,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6567,7 +6564,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18548-2024</t>
+          <t>A 64075-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6581,10 +6578,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45425</v>
+        <v>45279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6596,13 +6593,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6645,7 +6637,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 68894-2021</t>
+          <t>A 12787-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6659,10 +6651,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44526</v>
+        <v>46091</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6675,7 +6667,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6718,7 +6710,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13046-2022</t>
+          <t>A 42975-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,10 +6724,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44643</v>
+        <v>46310</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6748,7 +6740,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6791,7 +6783,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8078-2024</t>
+          <t>A 18512-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6805,10 +6797,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45351</v>
+        <v>45425</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6826,7 +6818,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6869,7 +6861,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24873-2023</t>
+          <t>A 32486-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6883,10 +6875,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45085</v>
+        <v>46239</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6899,7 +6891,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6942,7 +6934,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23666-2024</t>
+          <t>A 18528-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6956,10 +6948,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45454</v>
+        <v>45425</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6971,8 +6963,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7015,7 +7012,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9946-2024</t>
+          <t>A 18490-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7029,10 +7026,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7045,7 +7042,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7088,7 +7085,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32486-2026</t>
+          <t>A 18548-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7102,10 +7099,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46239</v>
+        <v>45425</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7117,8 +7114,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7161,7 +7163,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52836-2024</t>
+          <t>A 42392-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7175,10 +7177,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45610</v>
+        <v>46307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7191,7 +7193,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7234,7 +7236,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5474-2024</t>
+          <t>A 20839-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7248,10 +7250,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45333</v>
+        <v>45439</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7263,13 +7265,8 @@
           <t>HANINGE</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7312,7 +7309,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14900-2025</t>
+          <t>A 5474-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7326,10 +7323,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45743</v>
+        <v>45333</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7341,8 +7338,13 @@
           <t>HANINGE</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7385,7 +7387,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42392-2026</t>
+          <t>A 23666-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7399,10 +7401,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46307</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7415,7 +7417,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7475,7 +7477,7 @@
         <v>46310</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7531,7 +7533,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42975-2026</t>
+          <t>A 68896-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7545,10 +7547,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46310</v>
+        <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7561,7 +7563,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7621,7 +7623,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt HANINGE.xlsx
+++ b/Översikt HANINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44518</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46043</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -821,19 +821,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" t="n">
         <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -855,6 +855,7 @@
 Motaggsvamp
 Nordfladdermus
 Orange taggsvamp
+Phellodon aquiloniniger
 Skarp dropptaggsvamp
 Svartvit taggsvamp
 Tallkötticka
@@ -961,7 +962,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1133,7 +1134,7 @@
         <v>45394</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1291,7 +1292,7 @@
         <v>45258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1429,7 +1430,7 @@
         <v>44525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1564,7 @@
         <v>44525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1694,7 @@
         <v>46171</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1826,7 +1827,7 @@
         <v>45469</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1955,7 +1956,7 @@
         <v>45991</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2087,7 +2088,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2218,7 +2219,7 @@
         <v>45991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2344,7 +2345,7 @@
         <v>45679</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2463,7 +2464,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2573,7 +2574,7 @@
         <v>45203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2682,7 +2683,7 @@
         <v>46199</v>